--- a/docs/FORM_TEST_OPEN_WEBUI_v2.xlsx
+++ b/docs/FORM_TEST_OPEN_WEBUI_v2.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tổng hợp" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Form Test Tính Năng'!$A$3:$M$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Form Test Tính Năng'!$A$3:$M$108</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Form Test Nghiệp Vụ'!$A$3:$N$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1192,7 +1192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M150"/>
+  <dimension ref="A1:M158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1232,7 +1232,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Phiên bản: v2.0  |  Ngày: 01/04/2026  |  URL: https://openwebui.rangdong.com.vn  |  Tổng: 95 test cases</t>
+          <t>Phiên bản: v2.1  |  Ngày: 06/04/2026  |  URL: https://openwebui.rangdong.com.vn  |  Tổng: 103 test cases  |  4 providers: OpenAI, Google, xAI, Anthropic</t>
         </is>
       </c>
     </row>
@@ -2120,17 +2120,17 @@
       </c>
       <c r="D26" s="17" t="inlineStr">
         <is>
-          <t>Tạo ảnh DALL-E 3</t>
+          <t>GPT Image 1.5 (OpenAI)</t>
         </is>
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t>Chọn img-gpt-dalle-3, gõ mô tả</t>
+          <t>Chọn model gpt-image-1.5, gõ: "Vẽ con mèo trên bàn làm việc"</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>Ảnh tạo đúng mô tả</t>
+          <t>Ảnh tạo đúng mô tả, chất lượng cao</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr"/>
@@ -2157,17 +2157,17 @@
       </c>
       <c r="D27" s="17" t="inlineStr">
         <is>
-          <t>Tạo ảnh Gemini Flash</t>
+          <t>GPT Image 1 (OpenAI)</t>
         </is>
       </c>
       <c r="E27" s="17" t="inlineStr">
         <is>
-          <t>Chọn img-gemini-flash, gõ mô tả</t>
+          <t>Chọn model gpt-image-1, gõ mô tả ảnh</t>
         </is>
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>Ảnh tạo nhanh, chất lượng OK</t>
+          <t>Ảnh tạo đúng mô tả</t>
         </is>
       </c>
       <c r="G27" s="17" t="inlineStr"/>
@@ -2194,17 +2194,17 @@
       </c>
       <c r="D28" s="17" t="inlineStr">
         <is>
-          <t>Tạo ảnh Gemini Pro</t>
+          <t>Gemini 3.1 Flash Image</t>
         </is>
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t>Chọn img-gemini-pro, gõ mô tả</t>
+          <t>Chọn model gemini-3.1-flash-image-preview, gõ mô tả</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>Ảnh chất lượng cao, chi tiết tốt</t>
+          <t>Ảnh tạo nhanh, chất lượng OK</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr"/>
@@ -2231,17 +2231,17 @@
       </c>
       <c r="D29" s="17" t="inlineStr">
         <is>
-          <t>Sửa ảnh nhiều lượt</t>
+          <t>Gemini 3 Pro Image</t>
         </is>
       </c>
       <c r="E29" s="17" t="inlineStr">
         <is>
-          <t>L1: Vẽ → L2: Thêm chi tiết → L3: Đổi style</t>
+          <t>Chọn model gemini-3-pro-image-preview, gõ mô tả</t>
         </is>
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>Mỗi lượt chỉnh dựa trên ảnh trước</t>
+          <t>Ảnh chất lượng cao, chi tiết tốt</t>
         </is>
       </c>
       <c r="G29" s="17" t="inlineStr"/>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="D30" s="17" t="inlineStr">
         <is>
-          <t>Tạo ảnh phức tạp</t>
+          <t>Grok Imagine</t>
         </is>
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t>Gõ mô tả dài, nhiều chi tiết</t>
+          <t>Chọn model grok-imagine-image, gõ mô tả</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>Ảnh phản ánh đầy đủ mô tả</t>
+          <t>Ảnh tạo đúng mô tả (xAI)</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr"/>
@@ -2305,17 +2305,17 @@
       </c>
       <c r="D31" s="17" t="inlineStr">
         <is>
-          <t>Prompt tiếng Việt</t>
+          <t>Grok Imagine Pro</t>
         </is>
       </c>
       <c r="E31" s="17" t="inlineStr">
         <is>
-          <t>Gõ prompt bằng tiếng Việt</t>
+          <t>Chọn model grok-imagine-image-pro, gõ mô tả</t>
         </is>
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>Hiểu và tạo ảnh đúng</t>
+          <t>Ảnh chất lượng cao hơn, nhanh hơn</t>
         </is>
       </c>
       <c r="G31" s="17" t="inlineStr"/>
@@ -2327,115 +2327,115 @@
       <c r="M31" s="17" t="inlineStr"/>
     </row>
     <row r="32" ht="40" customHeight="1">
-      <c r="A32" s="19" t="n">
+      <c r="A32" s="16" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="inlineStr">
-        <is>
-          <t>Gửi file &amp; truy xuất</t>
-        </is>
-      </c>
-      <c r="D32" s="20" t="inlineStr">
-        <is>
-          <t>Upload PDF</t>
-        </is>
-      </c>
-      <c r="E32" s="20" t="inlineStr">
-        <is>
-          <t>Gửi file PDF ~5 trang + hỏi nội dung</t>
-        </is>
-      </c>
-      <c r="F32" s="20" t="inlineStr">
-        <is>
-          <t>AI đọc và trả lời chính xác</t>
-        </is>
-      </c>
-      <c r="G32" s="20" t="inlineStr"/>
-      <c r="H32" s="20" t="inlineStr"/>
-      <c r="I32" s="19" t="inlineStr"/>
-      <c r="J32" s="19" t="inlineStr"/>
-      <c r="K32" s="21" t="inlineStr"/>
-      <c r="L32" s="20" t="inlineStr"/>
-      <c r="M32" s="20" t="inlineStr"/>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>Tạo ảnh AI</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>Sửa ảnh nhiều lượt</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>L1: Vẽ → L2: Thêm chi tiết → L3: Đổi style</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>Mỗi lượt chỉnh dựa trên ảnh trước</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr"/>
+      <c r="H32" s="17" t="inlineStr"/>
+      <c r="I32" s="16" t="inlineStr"/>
+      <c r="J32" s="16" t="inlineStr"/>
+      <c r="K32" s="18" t="inlineStr"/>
+      <c r="L32" s="17" t="inlineStr"/>
+      <c r="M32" s="17" t="inlineStr"/>
     </row>
     <row r="33" ht="40" customHeight="1">
-      <c r="A33" s="19" t="n">
+      <c r="A33" s="16" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="inlineStr">
-        <is>
-          <t>Gửi file &amp; truy xuất</t>
-        </is>
-      </c>
-      <c r="D33" s="20" t="inlineStr">
-        <is>
-          <t>Upload Word</t>
-        </is>
-      </c>
-      <c r="E33" s="20" t="inlineStr">
-        <is>
-          <t>Gửi file .docx + hỏi tóm tắt</t>
-        </is>
-      </c>
-      <c r="F33" s="20" t="inlineStr">
-        <is>
-          <t>Tóm tắt đúng, đầy đủ ý chính</t>
-        </is>
-      </c>
-      <c r="G33" s="20" t="inlineStr"/>
-      <c r="H33" s="20" t="inlineStr"/>
-      <c r="I33" s="19" t="inlineStr"/>
-      <c r="J33" s="19" t="inlineStr"/>
-      <c r="K33" s="21" t="inlineStr"/>
-      <c r="L33" s="20" t="inlineStr"/>
-      <c r="M33" s="20" t="inlineStr"/>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>Tạo ảnh AI</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>Tạo ảnh phức tạp</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>Gõ mô tả dài, nhiều chi tiết cụ thể</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>Ảnh phản ánh đầy đủ mô tả</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr"/>
+      <c r="H33" s="17" t="inlineStr"/>
+      <c r="I33" s="16" t="inlineStr"/>
+      <c r="J33" s="16" t="inlineStr"/>
+      <c r="K33" s="18" t="inlineStr"/>
+      <c r="L33" s="17" t="inlineStr"/>
+      <c r="M33" s="17" t="inlineStr"/>
     </row>
     <row r="34" ht="40" customHeight="1">
-      <c r="A34" s="19" t="n">
+      <c r="A34" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="19" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="inlineStr">
-        <is>
-          <t>Gửi file &amp; truy xuất</t>
-        </is>
-      </c>
-      <c r="D34" s="20" t="inlineStr">
-        <is>
-          <t>Upload Excel</t>
-        </is>
-      </c>
-      <c r="E34" s="20" t="inlineStr">
-        <is>
-          <t>Gửi file Excel số liệu + hỏi tổng</t>
-        </is>
-      </c>
-      <c r="F34" s="20" t="inlineStr">
-        <is>
-          <t>Đọc số liệu, trả lời đúng</t>
-        </is>
-      </c>
-      <c r="G34" s="20" t="inlineStr"/>
-      <c r="H34" s="20" t="inlineStr"/>
-      <c r="I34" s="19" t="inlineStr"/>
-      <c r="J34" s="19" t="inlineStr"/>
-      <c r="K34" s="21" t="inlineStr"/>
-      <c r="L34" s="20" t="inlineStr"/>
-      <c r="M34" s="20" t="inlineStr"/>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>Tạo ảnh AI</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>Prompt tiếng Việt</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>Gõ prompt bằng tiếng Việt</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>Hiểu và tạo ảnh đúng</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr"/>
+      <c r="H34" s="17" t="inlineStr"/>
+      <c r="I34" s="16" t="inlineStr"/>
+      <c r="J34" s="16" t="inlineStr"/>
+      <c r="K34" s="18" t="inlineStr"/>
+      <c r="L34" s="17" t="inlineStr"/>
+      <c r="M34" s="17" t="inlineStr"/>
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" s="19" t="n">
@@ -2453,17 +2453,17 @@
       </c>
       <c r="D35" s="20" t="inlineStr">
         <is>
-          <t>Upload CSV</t>
+          <t>Upload PDF</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
         <is>
-          <t>Gửi file CSV + hỏi thông tin</t>
+          <t>Gửi file PDF ~5 trang + hỏi nội dung</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
         <is>
-          <t>Đọc đúng, trả lời chính xác</t>
+          <t>AI đọc và trả lời chính xác</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr"/>
@@ -2490,17 +2490,17 @@
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>Upload TXT</t>
+          <t>Upload Word</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>Gửi file .txt + hỏi nội dung</t>
+          <t>Gửi file .docx + hỏi tóm tắt</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
-          <t>Đọc và trả lời đúng</t>
+          <t>Tóm tắt đúng, đầy đủ ý chính</t>
         </is>
       </c>
       <c r="G36" s="20" t="inlineStr"/>
@@ -2527,17 +2527,17 @@
       </c>
       <c r="D37" s="20" t="inlineStr">
         <is>
-          <t>Upload nhiều file</t>
+          <t>Upload Excel</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
         <is>
-          <t>Gửi 3 file khác định dạng cùng lúc</t>
+          <t>Gửi file Excel số liệu + hỏi tổng</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
         <is>
-          <t>Xử lý tất cả, trả lời liên quan</t>
+          <t>Đọc số liệu, trả lời đúng</t>
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr"/>
@@ -2564,17 +2564,17 @@
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>Upload file lớn</t>
+          <t>Upload CSV</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>Gửi file PDF ~20-30MB</t>
+          <t>Gửi file CSV + hỏi thông tin</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
-          <t>Thành công hoặc báo lỗi rõ ràng</t>
+          <t>Đọc đúng, trả lời chính xác</t>
         </is>
       </c>
       <c r="G38" s="20" t="inlineStr"/>
@@ -2601,17 +2601,17 @@
       </c>
       <c r="D39" s="20" t="inlineStr">
         <is>
-          <t>Hỏi đáp sâu file</t>
+          <t>Upload TXT</t>
         </is>
       </c>
       <c r="E39" s="20" t="inlineStr">
         <is>
-          <t>Upload → hỏi 3-4 câu liên tiếp</t>
+          <t>Gửi file .txt + hỏi nội dung</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
         <is>
-          <t>AI nhớ file, trả lời chính xác</t>
+          <t>Đọc và trả lời đúng</t>
         </is>
       </c>
       <c r="G39" s="20" t="inlineStr"/>
@@ -2638,17 +2638,17 @@
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>Upload HTML</t>
+          <t>Upload nhiều file</t>
         </is>
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>Gửi file .html + hỏi</t>
+          <t>Gửi 3 file khác định dạng cùng lúc</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
         <is>
-          <t>Đọc được nội dung text</t>
+          <t>Xử lý tất cả, trả lời liên quan</t>
         </is>
       </c>
       <c r="G40" s="20" t="inlineStr"/>
@@ -2675,17 +2675,17 @@
       </c>
       <c r="D41" s="20" t="inlineStr">
         <is>
-          <t>Trích dẫn nguồn</t>
+          <t>Upload file lớn</t>
         </is>
       </c>
       <c r="E41" s="20" t="inlineStr">
         <is>
-          <t>Hỏi từ file đã upload</t>
+          <t>Gửi file PDF ~20-30MB</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
         <is>
-          <t>Trích dẫn tên file, trang nguồn</t>
+          <t>Thành công hoặc báo lỗi rõ ràng</t>
         </is>
       </c>
       <c r="G41" s="20" t="inlineStr"/>
@@ -2697,115 +2697,115 @@
       <c r="M41" s="20" t="inlineStr"/>
     </row>
     <row r="42" ht="40" customHeight="1">
-      <c r="A42" s="22" t="n">
+      <c r="A42" s="19" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="22" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C42" s="23" t="inlineStr">
-        <is>
-          <t>Chọn Model</t>
-        </is>
-      </c>
-      <c r="D42" s="23" t="inlineStr">
-        <is>
-          <t>Danh sách model</t>
-        </is>
-      </c>
-      <c r="E42" s="23" t="inlineStr">
-        <is>
-          <t>Mở dropdown chọn model</t>
-        </is>
-      </c>
-      <c r="F42" s="23" t="inlineStr">
-        <is>
-          <t>Hiển thị đầy đủ tất cả model</t>
-        </is>
-      </c>
-      <c r="G42" s="23" t="inlineStr"/>
-      <c r="H42" s="23" t="inlineStr"/>
-      <c r="I42" s="22" t="inlineStr"/>
-      <c r="J42" s="22" t="inlineStr"/>
-      <c r="K42" s="24" t="inlineStr"/>
-      <c r="L42" s="23" t="inlineStr"/>
-      <c r="M42" s="23" t="inlineStr"/>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>Gửi file &amp; truy xuất</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>Hỏi đáp sâu file</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>Upload → hỏi 3-4 câu liên tiếp</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>AI nhớ file, trả lời chính xác</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr"/>
+      <c r="H42" s="20" t="inlineStr"/>
+      <c r="I42" s="19" t="inlineStr"/>
+      <c r="J42" s="19" t="inlineStr"/>
+      <c r="K42" s="21" t="inlineStr"/>
+      <c r="L42" s="20" t="inlineStr"/>
+      <c r="M42" s="20" t="inlineStr"/>
     </row>
     <row r="43" ht="40" customHeight="1">
-      <c r="A43" s="22" t="n">
+      <c r="A43" s="19" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="22" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C43" s="23" t="inlineStr">
-        <is>
-          <t>Chọn Model</t>
-        </is>
-      </c>
-      <c r="D43" s="23" t="inlineStr">
-        <is>
-          <t>GPT-5</t>
-        </is>
-      </c>
-      <c r="E43" s="23" t="inlineStr">
-        <is>
-          <t>Chọn GPT-5 → hỏi 1 câu</t>
-        </is>
-      </c>
-      <c r="F43" s="23" t="inlineStr">
-        <is>
-          <t>Trả lời thành công, chất lượng cao</t>
-        </is>
-      </c>
-      <c r="G43" s="23" t="inlineStr"/>
-      <c r="H43" s="23" t="inlineStr"/>
-      <c r="I43" s="22" t="inlineStr"/>
-      <c r="J43" s="22" t="inlineStr"/>
-      <c r="K43" s="24" t="inlineStr"/>
-      <c r="L43" s="23" t="inlineStr"/>
-      <c r="M43" s="23" t="inlineStr"/>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>Gửi file &amp; truy xuất</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>Upload HTML</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>Gửi file .html + hỏi</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>Đọc được nội dung text</t>
+        </is>
+      </c>
+      <c r="G43" s="20" t="inlineStr"/>
+      <c r="H43" s="20" t="inlineStr"/>
+      <c r="I43" s="19" t="inlineStr"/>
+      <c r="J43" s="19" t="inlineStr"/>
+      <c r="K43" s="21" t="inlineStr"/>
+      <c r="L43" s="20" t="inlineStr"/>
+      <c r="M43" s="20" t="inlineStr"/>
     </row>
     <row r="44" ht="40" customHeight="1">
-      <c r="A44" s="22" t="n">
+      <c r="A44" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="22" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C44" s="23" t="inlineStr">
-        <is>
-          <t>Chọn Model</t>
-        </is>
-      </c>
-      <c r="D44" s="23" t="inlineStr">
-        <is>
-          <t>GPT-5 Mini</t>
-        </is>
-      </c>
-      <c r="E44" s="23" t="inlineStr">
-        <is>
-          <t>Chọn GPT-5 Mini → hỏi 1 câu</t>
-        </is>
-      </c>
-      <c r="F44" s="23" t="inlineStr">
-        <is>
-          <t>Trả lời nhanh, chất lượng tốt</t>
-        </is>
-      </c>
-      <c r="G44" s="23" t="inlineStr"/>
-      <c r="H44" s="23" t="inlineStr"/>
-      <c r="I44" s="22" t="inlineStr"/>
-      <c r="J44" s="22" t="inlineStr"/>
-      <c r="K44" s="24" t="inlineStr"/>
-      <c r="L44" s="23" t="inlineStr"/>
-      <c r="M44" s="23" t="inlineStr"/>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>Gửi file &amp; truy xuất</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>Trích dẫn nguồn</t>
+        </is>
+      </c>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t>Hỏi từ file đã upload</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>Trích dẫn tên file, trang nguồn</t>
+        </is>
+      </c>
+      <c r="G44" s="20" t="inlineStr"/>
+      <c r="H44" s="20" t="inlineStr"/>
+      <c r="I44" s="19" t="inlineStr"/>
+      <c r="J44" s="19" t="inlineStr"/>
+      <c r="K44" s="21" t="inlineStr"/>
+      <c r="L44" s="20" t="inlineStr"/>
+      <c r="M44" s="20" t="inlineStr"/>
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" s="22" t="n">
@@ -2823,17 +2823,17 @@
       </c>
       <c r="D45" s="23" t="inlineStr">
         <is>
-          <t>GPT-4o</t>
+          <t>Danh sách model</t>
         </is>
       </c>
       <c r="E45" s="23" t="inlineStr">
         <is>
-          <t>Chọn GPT-4o → hỏi 1 câu</t>
+          <t>Mở dropdown chọn model</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t>Trả lời thành công</t>
+          <t>Hiển thị đầy đủ tất cả model (4 providers)</t>
         </is>
       </c>
       <c r="G45" s="23" t="inlineStr"/>
@@ -2860,17 +2860,17 @@
       </c>
       <c r="D46" s="23" t="inlineStr">
         <is>
-          <t>GPT-4.1</t>
+          <t>GPT-5.4 (OpenAI Flagship)</t>
         </is>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
-          <t>Chọn GPT-4.1 → hỏi 1 câu</t>
+          <t>Chọn gpt-5.4 → hỏi 1 câu</t>
         </is>
       </c>
       <c r="F46" s="23" t="inlineStr">
         <is>
-          <t>Trả lời thành công</t>
+          <t>Trả lời thành công, chất lượng cao nhất</t>
         </is>
       </c>
       <c r="G46" s="23" t="inlineStr"/>
@@ -2897,17 +2897,17 @@
       </c>
       <c r="D47" s="23" t="inlineStr">
         <is>
-          <t>Gemini 2.5 Pro</t>
+          <t>GPT-5.2 (OpenAI)</t>
         </is>
       </c>
       <c r="E47" s="23" t="inlineStr">
         <is>
-          <t>Chọn Gemini 2.5 Pro → hỏi 1 câu</t>
+          <t>Chọn gpt-5.2 → hỏi 1 câu</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t>Trả lời thành công, TV tốt</t>
+          <t>Trả lời nhanh, chất lượng tốt</t>
         </is>
       </c>
       <c r="G47" s="23" t="inlineStr"/>
@@ -2934,17 +2934,17 @@
       </c>
       <c r="D48" s="23" t="inlineStr">
         <is>
-          <t>Gemini 2.5 Flash</t>
+          <t>GPT-5 (OpenAI)</t>
         </is>
       </c>
       <c r="E48" s="23" t="inlineStr">
         <is>
-          <t>Chọn Gemini 2.5 Flash → hỏi 1 câu</t>
+          <t>Chọn gpt-5 → hỏi 1 câu</t>
         </is>
       </c>
       <c r="F48" s="23" t="inlineStr">
         <is>
-          <t>Trả lời nhanh, chất lượng ổn</t>
+          <t>Trả lời thành công, cân bằng giá/chất lượng</t>
         </is>
       </c>
       <c r="G48" s="23" t="inlineStr"/>
@@ -2971,17 +2971,17 @@
       </c>
       <c r="D49" s="23" t="inlineStr">
         <is>
-          <t>Gemini 3 Pro</t>
+          <t>Gemini 3.1 Pro (Google)</t>
         </is>
       </c>
       <c r="E49" s="23" t="inlineStr">
         <is>
-          <t>Chọn Gemini 3 Pro → hỏi 1 câu</t>
+          <t>Chọn gemini-3.1-pro-preview → hỏi 1 câu</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t>Flagship mới nhất, trả lời tốt</t>
+          <t>Flagship Google, reasoning mạnh, TV tốt</t>
         </is>
       </c>
       <c r="G49" s="23" t="inlineStr"/>
@@ -3008,17 +3008,17 @@
       </c>
       <c r="D50" s="23" t="inlineStr">
         <is>
-          <t>Chuyển model giữa chừng</t>
+          <t>Gemini 3.1 Flash Lite (Google)</t>
         </is>
       </c>
       <c r="E50" s="23" t="inlineStr">
         <is>
-          <t>Chat GPT-5 → đổi Gemini → hỏi tiếp</t>
+          <t>Chọn gemini-3.1-flash-lite-preview → hỏi 1 câu</t>
         </is>
       </c>
       <c r="F50" s="23" t="inlineStr">
         <is>
-          <t>Hội thoại tiếp tục đúng</t>
+          <t>Trả lời nhanh, chi phí thấp</t>
         </is>
       </c>
       <c r="G50" s="23" t="inlineStr"/>
@@ -3045,17 +3045,17 @@
       </c>
       <c r="D51" s="23" t="inlineStr">
         <is>
-          <t>Model mặc định</t>
+          <t>Gemini 2.5 Flash (Google)</t>
         </is>
       </c>
       <c r="E51" s="23" t="inlineStr">
         <is>
-          <t>Settings → chọn model mặc định</t>
+          <t>Chọn gemini-2.5-flash → hỏi 1 câu</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t>Chat mới dùng model đã chọn</t>
+          <t>Trả lời nhanh, chất lượng ổn</t>
         </is>
       </c>
       <c r="G51" s="23" t="inlineStr"/>
@@ -3067,300 +3067,300 @@
       <c r="M51" s="23" t="inlineStr"/>
     </row>
     <row r="52" ht="40" customHeight="1">
-      <c r="A52" s="25" t="n">
+      <c r="A52" s="22" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="25" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C52" s="26" t="inlineStr">
-        <is>
-          <t>Kho kiến thức</t>
-        </is>
-      </c>
-      <c r="D52" s="26" t="inlineStr">
-        <is>
-          <t>Tạo Knowledge</t>
-        </is>
-      </c>
-      <c r="E52" s="26" t="inlineStr">
-        <is>
-          <t>Workspace → Knowledge → Create</t>
-        </is>
-      </c>
-      <c r="F52" s="26" t="inlineStr">
-        <is>
-          <t>Collection tạo thành công</t>
-        </is>
-      </c>
-      <c r="G52" s="26" t="inlineStr"/>
-      <c r="H52" s="26" t="inlineStr"/>
-      <c r="I52" s="25" t="inlineStr"/>
-      <c r="J52" s="25" t="inlineStr"/>
-      <c r="K52" s="27" t="inlineStr"/>
-      <c r="L52" s="26" t="inlineStr"/>
-      <c r="M52" s="26" t="inlineStr"/>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C52" s="23" t="inlineStr">
+        <is>
+          <t>Chọn Model</t>
+        </is>
+      </c>
+      <c r="D52" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.20 Reasoning (xAI)</t>
+        </is>
+      </c>
+      <c r="E52" s="23" t="inlineStr">
+        <is>
+          <t>Chọn grok-4.20-reasoning → hỏi 1 câu</t>
+        </is>
+      </c>
+      <c r="F52" s="23" t="inlineStr">
+        <is>
+          <t>Reasoning mạnh, trả lời chi tiết</t>
+        </is>
+      </c>
+      <c r="G52" s="23" t="inlineStr"/>
+      <c r="H52" s="23" t="inlineStr"/>
+      <c r="I52" s="22" t="inlineStr"/>
+      <c r="J52" s="22" t="inlineStr"/>
+      <c r="K52" s="24" t="inlineStr"/>
+      <c r="L52" s="23" t="inlineStr"/>
+      <c r="M52" s="23" t="inlineStr"/>
     </row>
     <row r="53" ht="40" customHeight="1">
-      <c r="A53" s="25" t="n">
+      <c r="A53" s="22" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="25" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C53" s="26" t="inlineStr">
-        <is>
-          <t>Kho kiến thức</t>
-        </is>
-      </c>
-      <c r="D53" s="26" t="inlineStr">
-        <is>
-          <t>Upload PDF</t>
-        </is>
-      </c>
-      <c r="E53" s="26" t="inlineStr">
-        <is>
-          <t>Upload file PDF ~5MB vào Knowledge</t>
-        </is>
-      </c>
-      <c r="F53" s="26" t="inlineStr">
-        <is>
-          <t>Upload thành công, được index</t>
-        </is>
-      </c>
-      <c r="G53" s="26" t="inlineStr"/>
-      <c r="H53" s="26" t="inlineStr"/>
-      <c r="I53" s="25" t="inlineStr"/>
-      <c r="J53" s="25" t="inlineStr"/>
-      <c r="K53" s="27" t="inlineStr"/>
-      <c r="L53" s="26" t="inlineStr"/>
-      <c r="M53" s="26" t="inlineStr"/>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="inlineStr">
+        <is>
+          <t>Chọn Model</t>
+        </is>
+      </c>
+      <c r="D53" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4-1 Fast (xAI)</t>
+        </is>
+      </c>
+      <c r="E53" s="23" t="inlineStr">
+        <is>
+          <t>Chọn grok-4-1-fast-reasoning → hỏi 1 câu</t>
+        </is>
+      </c>
+      <c r="F53" s="23" t="inlineStr">
+        <is>
+          <t>Trả lời nhanh, chi phí thấp</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="inlineStr"/>
+      <c r="H53" s="23" t="inlineStr"/>
+      <c r="I53" s="22" t="inlineStr"/>
+      <c r="J53" s="22" t="inlineStr"/>
+      <c r="K53" s="24" t="inlineStr"/>
+      <c r="L53" s="23" t="inlineStr"/>
+      <c r="M53" s="23" t="inlineStr"/>
     </row>
     <row r="54" ht="40" customHeight="1">
-      <c r="A54" s="25" t="n">
+      <c r="A54" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="25" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C54" s="26" t="inlineStr">
-        <is>
-          <t>Kho kiến thức</t>
-        </is>
-      </c>
-      <c r="D54" s="26" t="inlineStr">
-        <is>
-          <t>Upload Word</t>
-        </is>
-      </c>
-      <c r="E54" s="26" t="inlineStr">
-        <is>
-          <t>Upload file .docx vào Knowledge</t>
-        </is>
-      </c>
-      <c r="F54" s="26" t="inlineStr">
-        <is>
-          <t>Upload thành công</t>
-        </is>
-      </c>
-      <c r="G54" s="26" t="inlineStr"/>
-      <c r="H54" s="26" t="inlineStr"/>
-      <c r="I54" s="25" t="inlineStr"/>
-      <c r="J54" s="25" t="inlineStr"/>
-      <c r="K54" s="27" t="inlineStr"/>
-      <c r="L54" s="26" t="inlineStr"/>
-      <c r="M54" s="26" t="inlineStr"/>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="inlineStr">
+        <is>
+          <t>Chọn Model</t>
+        </is>
+      </c>
+      <c r="D54" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4-1 Fast Lite (xAI)</t>
+        </is>
+      </c>
+      <c r="E54" s="23" t="inlineStr">
+        <is>
+          <t>Chọn grok-4-1-fast-non-reasoning → hỏi 1 câu</t>
+        </is>
+      </c>
+      <c r="F54" s="23" t="inlineStr">
+        <is>
+          <t>Fastest, no reasoning, chi phí thấp nhất</t>
+        </is>
+      </c>
+      <c r="G54" s="23" t="inlineStr"/>
+      <c r="H54" s="23" t="inlineStr"/>
+      <c r="I54" s="22" t="inlineStr"/>
+      <c r="J54" s="22" t="inlineStr"/>
+      <c r="K54" s="24" t="inlineStr"/>
+      <c r="L54" s="23" t="inlineStr"/>
+      <c r="M54" s="23" t="inlineStr"/>
     </row>
     <row r="55" ht="40" customHeight="1">
-      <c r="A55" s="25" t="n">
+      <c r="A55" s="22" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="25" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C55" s="26" t="inlineStr">
-        <is>
-          <t>Kho kiến thức</t>
-        </is>
-      </c>
-      <c r="D55" s="26" t="inlineStr">
-        <is>
-          <t>Upload Excel</t>
-        </is>
-      </c>
-      <c r="E55" s="26" t="inlineStr">
-        <is>
-          <t>Upload file .xlsx vào Knowledge</t>
-        </is>
-      </c>
-      <c r="F55" s="26" t="inlineStr">
-        <is>
-          <t>Upload thành công</t>
-        </is>
-      </c>
-      <c r="G55" s="26" t="inlineStr"/>
-      <c r="H55" s="26" t="inlineStr"/>
-      <c r="I55" s="25" t="inlineStr"/>
-      <c r="J55" s="25" t="inlineStr"/>
-      <c r="K55" s="27" t="inlineStr"/>
-      <c r="L55" s="26" t="inlineStr"/>
-      <c r="M55" s="26" t="inlineStr"/>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C55" s="23" t="inlineStr">
+        <is>
+          <t>Chọn Model</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.6 (Anthropic)</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="inlineStr">
+        <is>
+          <t>Chọn claude-opus-4-6 → hỏi 1 câu</t>
+        </is>
+      </c>
+      <c r="F55" s="23" t="inlineStr">
+        <is>
+          <t>Flagship Anthropic, chất lượng cao</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr"/>
+      <c r="H55" s="23" t="inlineStr"/>
+      <c r="I55" s="22" t="inlineStr"/>
+      <c r="J55" s="22" t="inlineStr"/>
+      <c r="K55" s="24" t="inlineStr"/>
+      <c r="L55" s="23" t="inlineStr"/>
+      <c r="M55" s="23" t="inlineStr"/>
     </row>
     <row r="56" ht="40" customHeight="1">
-      <c r="A56" s="25" t="n">
+      <c r="A56" s="22" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="25" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C56" s="26" t="inlineStr">
-        <is>
-          <t>Kho kiến thức</t>
-        </is>
-      </c>
-      <c r="D56" s="26" t="inlineStr">
-        <is>
-          <t>Upload CSV</t>
-        </is>
-      </c>
-      <c r="E56" s="26" t="inlineStr">
-        <is>
-          <t>Upload file .csv vào Knowledge</t>
-        </is>
-      </c>
-      <c r="F56" s="26" t="inlineStr">
-        <is>
-          <t>Upload thành công</t>
-        </is>
-      </c>
-      <c r="G56" s="26" t="inlineStr"/>
-      <c r="H56" s="26" t="inlineStr"/>
-      <c r="I56" s="25" t="inlineStr"/>
-      <c r="J56" s="25" t="inlineStr"/>
-      <c r="K56" s="27" t="inlineStr"/>
-      <c r="L56" s="26" t="inlineStr"/>
-      <c r="M56" s="26" t="inlineStr"/>
+      <c r="B56" s="22" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C56" s="23" t="inlineStr">
+        <is>
+          <t>Chọn Model</t>
+        </is>
+      </c>
+      <c r="D56" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.6 (Anthropic)</t>
+        </is>
+      </c>
+      <c r="E56" s="23" t="inlineStr">
+        <is>
+          <t>Chọn claude-sonnet-4-6 → hỏi 1 câu</t>
+        </is>
+      </c>
+      <c r="F56" s="23" t="inlineStr">
+        <is>
+          <t>Cân bằng giá/chất lượng</t>
+        </is>
+      </c>
+      <c r="G56" s="23" t="inlineStr"/>
+      <c r="H56" s="23" t="inlineStr"/>
+      <c r="I56" s="22" t="inlineStr"/>
+      <c r="J56" s="22" t="inlineStr"/>
+      <c r="K56" s="24" t="inlineStr"/>
+      <c r="L56" s="23" t="inlineStr"/>
+      <c r="M56" s="23" t="inlineStr"/>
     </row>
     <row r="57" ht="40" customHeight="1">
-      <c r="A57" s="25" t="n">
+      <c r="A57" s="22" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="25" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C57" s="26" t="inlineStr">
-        <is>
-          <t>Kho kiến thức</t>
-        </is>
-      </c>
-      <c r="D57" s="26" t="inlineStr">
-        <is>
-          <t>Upload nhiều file</t>
-        </is>
-      </c>
-      <c r="E57" s="26" t="inlineStr">
-        <is>
-          <t>Upload 5+ file khác nhau vào 1 Knowledge</t>
-        </is>
-      </c>
-      <c r="F57" s="26" t="inlineStr">
-        <is>
-          <t>Tất cả upload thành công</t>
-        </is>
-      </c>
-      <c r="G57" s="26" t="inlineStr"/>
-      <c r="H57" s="26" t="inlineStr"/>
-      <c r="I57" s="25" t="inlineStr"/>
-      <c r="J57" s="25" t="inlineStr"/>
-      <c r="K57" s="27" t="inlineStr"/>
-      <c r="L57" s="26" t="inlineStr"/>
-      <c r="M57" s="26" t="inlineStr"/>
+      <c r="B57" s="22" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C57" s="23" t="inlineStr">
+        <is>
+          <t>Chọn Model</t>
+        </is>
+      </c>
+      <c r="D57" s="23" t="inlineStr">
+        <is>
+          <t>Claude Haiku 4.5 (Anthropic)</t>
+        </is>
+      </c>
+      <c r="E57" s="23" t="inlineStr">
+        <is>
+          <t>Chọn claude-haiku-4-5 → hỏi 1 câu</t>
+        </is>
+      </c>
+      <c r="F57" s="23" t="inlineStr">
+        <is>
+          <t>Trả lời nhanh, chi phí thấp</t>
+        </is>
+      </c>
+      <c r="G57" s="23" t="inlineStr"/>
+      <c r="H57" s="23" t="inlineStr"/>
+      <c r="I57" s="22" t="inlineStr"/>
+      <c r="J57" s="22" t="inlineStr"/>
+      <c r="K57" s="24" t="inlineStr"/>
+      <c r="L57" s="23" t="inlineStr"/>
+      <c r="M57" s="23" t="inlineStr"/>
     </row>
     <row r="58" ht="40" customHeight="1">
-      <c r="A58" s="25" t="n">
+      <c r="A58" s="22" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="25" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C58" s="26" t="inlineStr">
-        <is>
-          <t>Kho kiến thức</t>
-        </is>
-      </c>
-      <c r="D58" s="26" t="inlineStr">
-        <is>
-          <t>Upload file lớn</t>
-        </is>
-      </c>
-      <c r="E58" s="26" t="inlineStr">
-        <is>
-          <t>Upload file ~30-50MB</t>
-        </is>
-      </c>
-      <c r="F58" s="26" t="inlineStr">
-        <is>
-          <t>Thành công hoặc báo lỗi rõ</t>
-        </is>
-      </c>
-      <c r="G58" s="26" t="inlineStr"/>
-      <c r="H58" s="26" t="inlineStr"/>
-      <c r="I58" s="25" t="inlineStr"/>
-      <c r="J58" s="25" t="inlineStr"/>
-      <c r="K58" s="27" t="inlineStr"/>
-      <c r="L58" s="26" t="inlineStr"/>
-      <c r="M58" s="26" t="inlineStr"/>
+      <c r="B58" s="22" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C58" s="23" t="inlineStr">
+        <is>
+          <t>Chọn Model</t>
+        </is>
+      </c>
+      <c r="D58" s="23" t="inlineStr">
+        <is>
+          <t>Chuyển model giữa chừng</t>
+        </is>
+      </c>
+      <c r="E58" s="23" t="inlineStr">
+        <is>
+          <t>Chat gpt-5.4 → đổi claude-opus-4-6 → hỏi tiếp</t>
+        </is>
+      </c>
+      <c r="F58" s="23" t="inlineStr">
+        <is>
+          <t>Hội thoại tiếp tục đúng</t>
+        </is>
+      </c>
+      <c r="G58" s="23" t="inlineStr"/>
+      <c r="H58" s="23" t="inlineStr"/>
+      <c r="I58" s="22" t="inlineStr"/>
+      <c r="J58" s="22" t="inlineStr"/>
+      <c r="K58" s="24" t="inlineStr"/>
+      <c r="L58" s="23" t="inlineStr"/>
+      <c r="M58" s="23" t="inlineStr"/>
     </row>
     <row r="59" ht="40" customHeight="1">
-      <c r="A59" s="25" t="n">
+      <c r="A59" s="22" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="25" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C59" s="26" t="inlineStr">
-        <is>
-          <t>Kho kiến thức</t>
-        </is>
-      </c>
-      <c r="D59" s="26" t="inlineStr">
-        <is>
-          <t>Gọi Knowledge #</t>
-        </is>
-      </c>
-      <c r="E59" s="26" t="inlineStr">
-        <is>
-          <t>Trong chat gõ #tên-knowledge</t>
-        </is>
-      </c>
-      <c r="F59" s="26" t="inlineStr">
-        <is>
-          <t>Hiển thị gợi ý, chọn được</t>
-        </is>
-      </c>
-      <c r="G59" s="26" t="inlineStr"/>
-      <c r="H59" s="26" t="inlineStr"/>
-      <c r="I59" s="25" t="inlineStr"/>
-      <c r="J59" s="25" t="inlineStr"/>
-      <c r="K59" s="27" t="inlineStr"/>
-      <c r="L59" s="26" t="inlineStr"/>
-      <c r="M59" s="26" t="inlineStr"/>
+      <c r="B59" s="22" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C59" s="23" t="inlineStr">
+        <is>
+          <t>Chọn Model</t>
+        </is>
+      </c>
+      <c r="D59" s="23" t="inlineStr">
+        <is>
+          <t>Model mặc định</t>
+        </is>
+      </c>
+      <c r="E59" s="23" t="inlineStr">
+        <is>
+          <t>Settings → chọn model mặc định</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="inlineStr">
+        <is>
+          <t>Chat mới dùng model đã chọn</t>
+        </is>
+      </c>
+      <c r="G59" s="23" t="inlineStr"/>
+      <c r="H59" s="23" t="inlineStr"/>
+      <c r="I59" s="22" t="inlineStr"/>
+      <c r="J59" s="22" t="inlineStr"/>
+      <c r="K59" s="24" t="inlineStr"/>
+      <c r="L59" s="23" t="inlineStr"/>
+      <c r="M59" s="23" t="inlineStr"/>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" s="25" t="n">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="D60" s="26" t="inlineStr">
         <is>
-          <t>Hỏi đáp từ Knowledge</t>
+          <t>Tạo Knowledge</t>
         </is>
       </c>
       <c r="E60" s="26" t="inlineStr">
         <is>
-          <t>Gọi # rồi hỏi nội dung</t>
+          <t>Workspace → Knowledge → Create</t>
         </is>
       </c>
       <c r="F60" s="26" t="inlineStr">
         <is>
-          <t>Trả lời dựa trên Knowledge, trích dẫn</t>
+          <t>Collection tạo thành công</t>
         </is>
       </c>
       <c r="G60" s="26" t="inlineStr"/>
@@ -3415,17 +3415,17 @@
       </c>
       <c r="D61" s="26" t="inlineStr">
         <is>
-          <t>Xóa file</t>
+          <t>Upload PDF</t>
         </is>
       </c>
       <c r="E61" s="26" t="inlineStr">
         <is>
-          <t>Xóa 1 file trong Knowledge</t>
+          <t>Upload file PDF ~5MB vào Knowledge</t>
         </is>
       </c>
       <c r="F61" s="26" t="inlineStr">
         <is>
-          <t>File + embedding bị xóa</t>
+          <t>Upload thành công, được index</t>
         </is>
       </c>
       <c r="G61" s="26" t="inlineStr"/>
@@ -3452,17 +3452,17 @@
       </c>
       <c r="D62" s="26" t="inlineStr">
         <is>
-          <t>Xóa Knowledge</t>
+          <t>Upload Word</t>
         </is>
       </c>
       <c r="E62" s="26" t="inlineStr">
         <is>
-          <t>Xóa cả collection</t>
+          <t>Upload file .docx vào Knowledge</t>
         </is>
       </c>
       <c r="F62" s="26" t="inlineStr">
         <is>
-          <t>Collection + tất cả bị xóa</t>
+          <t>Upload thành công</t>
         </is>
       </c>
       <c r="G62" s="26" t="inlineStr"/>
@@ -3474,1416 +3474,1688 @@
       <c r="M62" s="26" t="inlineStr"/>
     </row>
     <row r="63" ht="40" customHeight="1">
-      <c r="A63" s="28" t="n">
+      <c r="A63" s="25" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="28" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C63" s="29" t="inlineStr">
+      <c r="B63" s="25" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C63" s="26" t="inlineStr">
+        <is>
+          <t>Kho kiến thức</t>
+        </is>
+      </c>
+      <c r="D63" s="26" t="inlineStr">
+        <is>
+          <t>Upload Excel</t>
+        </is>
+      </c>
+      <c r="E63" s="26" t="inlineStr">
+        <is>
+          <t>Upload file .xlsx vào Knowledge</t>
+        </is>
+      </c>
+      <c r="F63" s="26" t="inlineStr">
+        <is>
+          <t>Upload thành công</t>
+        </is>
+      </c>
+      <c r="G63" s="26" t="inlineStr"/>
+      <c r="H63" s="26" t="inlineStr"/>
+      <c r="I63" s="25" t="inlineStr"/>
+      <c r="J63" s="25" t="inlineStr"/>
+      <c r="K63" s="27" t="inlineStr"/>
+      <c r="L63" s="26" t="inlineStr"/>
+      <c r="M63" s="26" t="inlineStr"/>
+    </row>
+    <row r="64" ht="40" customHeight="1">
+      <c r="A64" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="25" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C64" s="26" t="inlineStr">
+        <is>
+          <t>Kho kiến thức</t>
+        </is>
+      </c>
+      <c r="D64" s="26" t="inlineStr">
+        <is>
+          <t>Upload CSV</t>
+        </is>
+      </c>
+      <c r="E64" s="26" t="inlineStr">
+        <is>
+          <t>Upload file .csv vào Knowledge</t>
+        </is>
+      </c>
+      <c r="F64" s="26" t="inlineStr">
+        <is>
+          <t>Upload thành công</t>
+        </is>
+      </c>
+      <c r="G64" s="26" t="inlineStr"/>
+      <c r="H64" s="26" t="inlineStr"/>
+      <c r="I64" s="25" t="inlineStr"/>
+      <c r="J64" s="25" t="inlineStr"/>
+      <c r="K64" s="27" t="inlineStr"/>
+      <c r="L64" s="26" t="inlineStr"/>
+      <c r="M64" s="26" t="inlineStr"/>
+    </row>
+    <row r="65" ht="40" customHeight="1">
+      <c r="A65" s="25" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="25" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C65" s="26" t="inlineStr">
+        <is>
+          <t>Kho kiến thức</t>
+        </is>
+      </c>
+      <c r="D65" s="26" t="inlineStr">
+        <is>
+          <t>Upload nhiều file</t>
+        </is>
+      </c>
+      <c r="E65" s="26" t="inlineStr">
+        <is>
+          <t>Upload 5+ file khác nhau vào 1 Knowledge</t>
+        </is>
+      </c>
+      <c r="F65" s="26" t="inlineStr">
+        <is>
+          <t>Tất cả upload thành công</t>
+        </is>
+      </c>
+      <c r="G65" s="26" t="inlineStr"/>
+      <c r="H65" s="26" t="inlineStr"/>
+      <c r="I65" s="25" t="inlineStr"/>
+      <c r="J65" s="25" t="inlineStr"/>
+      <c r="K65" s="27" t="inlineStr"/>
+      <c r="L65" s="26" t="inlineStr"/>
+      <c r="M65" s="26" t="inlineStr"/>
+    </row>
+    <row r="66" ht="40" customHeight="1">
+      <c r="A66" s="25" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="25" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C66" s="26" t="inlineStr">
+        <is>
+          <t>Kho kiến thức</t>
+        </is>
+      </c>
+      <c r="D66" s="26" t="inlineStr">
+        <is>
+          <t>Upload file lớn</t>
+        </is>
+      </c>
+      <c r="E66" s="26" t="inlineStr">
+        <is>
+          <t>Upload file ~30-50MB</t>
+        </is>
+      </c>
+      <c r="F66" s="26" t="inlineStr">
+        <is>
+          <t>Thành công hoặc báo lỗi rõ</t>
+        </is>
+      </c>
+      <c r="G66" s="26" t="inlineStr"/>
+      <c r="H66" s="26" t="inlineStr"/>
+      <c r="I66" s="25" t="inlineStr"/>
+      <c r="J66" s="25" t="inlineStr"/>
+      <c r="K66" s="27" t="inlineStr"/>
+      <c r="L66" s="26" t="inlineStr"/>
+      <c r="M66" s="26" t="inlineStr"/>
+    </row>
+    <row r="67" ht="40" customHeight="1">
+      <c r="A67" s="25" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="25" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C67" s="26" t="inlineStr">
+        <is>
+          <t>Kho kiến thức</t>
+        </is>
+      </c>
+      <c r="D67" s="26" t="inlineStr">
+        <is>
+          <t>Gọi Knowledge #</t>
+        </is>
+      </c>
+      <c r="E67" s="26" t="inlineStr">
+        <is>
+          <t>Trong chat gõ #tên-knowledge</t>
+        </is>
+      </c>
+      <c r="F67" s="26" t="inlineStr">
+        <is>
+          <t>Hiển thị gợi ý, chọn được</t>
+        </is>
+      </c>
+      <c r="G67" s="26" t="inlineStr"/>
+      <c r="H67" s="26" t="inlineStr"/>
+      <c r="I67" s="25" t="inlineStr"/>
+      <c r="J67" s="25" t="inlineStr"/>
+      <c r="K67" s="27" t="inlineStr"/>
+      <c r="L67" s="26" t="inlineStr"/>
+      <c r="M67" s="26" t="inlineStr"/>
+    </row>
+    <row r="68" ht="40" customHeight="1">
+      <c r="A68" s="25" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="25" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C68" s="26" t="inlineStr">
+        <is>
+          <t>Kho kiến thức</t>
+        </is>
+      </c>
+      <c r="D68" s="26" t="inlineStr">
+        <is>
+          <t>Hỏi đáp từ Knowledge</t>
+        </is>
+      </c>
+      <c r="E68" s="26" t="inlineStr">
+        <is>
+          <t>Gọi # rồi hỏi nội dung</t>
+        </is>
+      </c>
+      <c r="F68" s="26" t="inlineStr">
+        <is>
+          <t>Trả lời dựa trên Knowledge, trích dẫn</t>
+        </is>
+      </c>
+      <c r="G68" s="26" t="inlineStr"/>
+      <c r="H68" s="26" t="inlineStr"/>
+      <c r="I68" s="25" t="inlineStr"/>
+      <c r="J68" s="25" t="inlineStr"/>
+      <c r="K68" s="27" t="inlineStr"/>
+      <c r="L68" s="26" t="inlineStr"/>
+      <c r="M68" s="26" t="inlineStr"/>
+    </row>
+    <row r="69" ht="40" customHeight="1">
+      <c r="A69" s="25" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="25" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C69" s="26" t="inlineStr">
+        <is>
+          <t>Kho kiến thức</t>
+        </is>
+      </c>
+      <c r="D69" s="26" t="inlineStr">
+        <is>
+          <t>Xóa file</t>
+        </is>
+      </c>
+      <c r="E69" s="26" t="inlineStr">
+        <is>
+          <t>Xóa 1 file trong Knowledge</t>
+        </is>
+      </c>
+      <c r="F69" s="26" t="inlineStr">
+        <is>
+          <t>File + embedding bị xóa</t>
+        </is>
+      </c>
+      <c r="G69" s="26" t="inlineStr"/>
+      <c r="H69" s="26" t="inlineStr"/>
+      <c r="I69" s="25" t="inlineStr"/>
+      <c r="J69" s="25" t="inlineStr"/>
+      <c r="K69" s="27" t="inlineStr"/>
+      <c r="L69" s="26" t="inlineStr"/>
+      <c r="M69" s="26" t="inlineStr"/>
+    </row>
+    <row r="70" ht="40" customHeight="1">
+      <c r="A70" s="25" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="25" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C70" s="26" t="inlineStr">
+        <is>
+          <t>Kho kiến thức</t>
+        </is>
+      </c>
+      <c r="D70" s="26" t="inlineStr">
+        <is>
+          <t>Xóa Knowledge</t>
+        </is>
+      </c>
+      <c r="E70" s="26" t="inlineStr">
+        <is>
+          <t>Xóa cả collection</t>
+        </is>
+      </c>
+      <c r="F70" s="26" t="inlineStr">
+        <is>
+          <t>Collection + tất cả bị xóa</t>
+        </is>
+      </c>
+      <c r="G70" s="26" t="inlineStr"/>
+      <c r="H70" s="26" t="inlineStr"/>
+      <c r="I70" s="25" t="inlineStr"/>
+      <c r="J70" s="25" t="inlineStr"/>
+      <c r="K70" s="27" t="inlineStr"/>
+      <c r="L70" s="26" t="inlineStr"/>
+      <c r="M70" s="26" t="inlineStr"/>
+    </row>
+    <row r="71" ht="40" customHeight="1">
+      <c r="A71" s="28" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="28" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C71" s="29" t="inlineStr">
         <is>
           <t>Không gian làm việc</t>
         </is>
       </c>
-      <c r="D63" s="29" t="inlineStr">
+      <c r="D71" s="29" t="inlineStr">
         <is>
           <t>Tạo Workspace</t>
         </is>
       </c>
-      <c r="E63" s="29" t="inlineStr">
+      <c r="E71" s="29" t="inlineStr">
         <is>
           <t>Tạo Workspace mới</t>
         </is>
       </c>
-      <c r="F63" s="29" t="inlineStr">
+      <c r="F71" s="29" t="inlineStr">
         <is>
           <t>Workspace tạo thành công</t>
         </is>
       </c>
-      <c r="G63" s="29" t="inlineStr"/>
-      <c r="H63" s="29" t="inlineStr"/>
-      <c r="I63" s="28" t="inlineStr"/>
-      <c r="J63" s="28" t="inlineStr"/>
-      <c r="K63" s="30" t="inlineStr"/>
-      <c r="L63" s="29" t="inlineStr"/>
-      <c r="M63" s="29" t="inlineStr"/>
-    </row>
-    <row r="64" ht="40" customHeight="1">
-      <c r="A64" s="28" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="28" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C64" s="29" t="inlineStr">
+      <c r="G71" s="29" t="inlineStr"/>
+      <c r="H71" s="29" t="inlineStr"/>
+      <c r="I71" s="28" t="inlineStr"/>
+      <c r="J71" s="28" t="inlineStr"/>
+      <c r="K71" s="30" t="inlineStr"/>
+      <c r="L71" s="29" t="inlineStr"/>
+      <c r="M71" s="29" t="inlineStr"/>
+    </row>
+    <row r="72" ht="40" customHeight="1">
+      <c r="A72" s="28" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="28" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C72" s="29" t="inlineStr">
         <is>
           <t>Không gian làm việc</t>
         </is>
       </c>
-      <c r="D64" s="29" t="inlineStr">
+      <c r="D72" s="29" t="inlineStr">
         <is>
           <t>Chọn Workspace</t>
         </is>
       </c>
-      <c r="E64" s="29" t="inlineStr">
+      <c r="E72" s="29" t="inlineStr">
         <is>
           <t>Chuyển đổi giữa các Workspace</t>
         </is>
       </c>
-      <c r="F64" s="29" t="inlineStr">
+      <c r="F72" s="29" t="inlineStr">
         <is>
           <t>Chuyển mượt, dữ liệu riêng</t>
         </is>
       </c>
-      <c r="G64" s="29" t="inlineStr"/>
-      <c r="H64" s="29" t="inlineStr"/>
-      <c r="I64" s="28" t="inlineStr"/>
-      <c r="J64" s="28" t="inlineStr"/>
-      <c r="K64" s="30" t="inlineStr"/>
-      <c r="L64" s="29" t="inlineStr"/>
-      <c r="M64" s="29" t="inlineStr"/>
-    </row>
-    <row r="65" ht="40" customHeight="1">
-      <c r="A65" s="28" t="n">
-        <v>61</v>
-      </c>
-      <c r="B65" s="28" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C65" s="29" t="inlineStr">
+      <c r="G72" s="29" t="inlineStr"/>
+      <c r="H72" s="29" t="inlineStr"/>
+      <c r="I72" s="28" t="inlineStr"/>
+      <c r="J72" s="28" t="inlineStr"/>
+      <c r="K72" s="30" t="inlineStr"/>
+      <c r="L72" s="29" t="inlineStr"/>
+      <c r="M72" s="29" t="inlineStr"/>
+    </row>
+    <row r="73" ht="40" customHeight="1">
+      <c r="A73" s="28" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="28" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C73" s="29" t="inlineStr">
         <is>
           <t>Không gian làm việc</t>
         </is>
       </c>
-      <c r="D65" s="29" t="inlineStr">
+      <c r="D73" s="29" t="inlineStr">
         <is>
           <t>Chia sẻ Knowledge</t>
         </is>
       </c>
-      <c r="E65" s="29" t="inlineStr">
+      <c r="E73" s="29" t="inlineStr">
         <is>
           <t>Chia sẻ Knowledge cho user khác</t>
         </is>
       </c>
-      <c r="F65" s="29" t="inlineStr">
+      <c r="F73" s="29" t="inlineStr">
         <is>
           <t>User khác truy cập được</t>
         </is>
       </c>
-      <c r="G65" s="29" t="inlineStr"/>
-      <c r="H65" s="29" t="inlineStr"/>
-      <c r="I65" s="28" t="inlineStr"/>
-      <c r="J65" s="28" t="inlineStr"/>
-      <c r="K65" s="30" t="inlineStr"/>
-      <c r="L65" s="29" t="inlineStr"/>
-      <c r="M65" s="29" t="inlineStr"/>
-    </row>
-    <row r="66" ht="40" customHeight="1">
-      <c r="A66" s="28" t="n">
-        <v>62</v>
-      </c>
-      <c r="B66" s="28" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C66" s="29" t="inlineStr">
+      <c r="G73" s="29" t="inlineStr"/>
+      <c r="H73" s="29" t="inlineStr"/>
+      <c r="I73" s="28" t="inlineStr"/>
+      <c r="J73" s="28" t="inlineStr"/>
+      <c r="K73" s="30" t="inlineStr"/>
+      <c r="L73" s="29" t="inlineStr"/>
+      <c r="M73" s="29" t="inlineStr"/>
+    </row>
+    <row r="74" ht="40" customHeight="1">
+      <c r="A74" s="28" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="28" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C74" s="29" t="inlineStr">
         <is>
           <t>Không gian làm việc</t>
         </is>
       </c>
-      <c r="D66" s="29" t="inlineStr">
+      <c r="D74" s="29" t="inlineStr">
         <is>
           <t>Access control</t>
         </is>
       </c>
-      <c r="E66" s="29" t="inlineStr">
+      <c r="E74" s="29" t="inlineStr">
         <is>
           <t>Giới hạn quyền truy cập</t>
         </is>
       </c>
-      <c r="F66" s="29" t="inlineStr">
+      <c r="F74" s="29" t="inlineStr">
         <is>
           <t>Chỉ user được phép mới truy cập</t>
         </is>
       </c>
-      <c r="G66" s="29" t="inlineStr"/>
-      <c r="H66" s="29" t="inlineStr"/>
-      <c r="I66" s="28" t="inlineStr"/>
-      <c r="J66" s="28" t="inlineStr"/>
-      <c r="K66" s="30" t="inlineStr"/>
-      <c r="L66" s="29" t="inlineStr"/>
-      <c r="M66" s="29" t="inlineStr"/>
-    </row>
-    <row r="67" ht="40" customHeight="1">
-      <c r="A67" s="31" t="n">
-        <v>63</v>
-      </c>
-      <c r="B67" s="31" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C67" s="32" t="inlineStr">
+      <c r="G74" s="29" t="inlineStr"/>
+      <c r="H74" s="29" t="inlineStr"/>
+      <c r="I74" s="28" t="inlineStr"/>
+      <c r="J74" s="28" t="inlineStr"/>
+      <c r="K74" s="30" t="inlineStr"/>
+      <c r="L74" s="29" t="inlineStr"/>
+      <c r="M74" s="29" t="inlineStr"/>
+    </row>
+    <row r="75" ht="40" customHeight="1">
+      <c r="A75" s="31" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="31" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C75" s="32" t="inlineStr">
         <is>
           <t>Giọng nói</t>
         </is>
       </c>
-      <c r="D67" s="32" t="inlineStr">
+      <c r="D75" s="32" t="inlineStr">
         <is>
           <t>Text-to-Speech</t>
         </is>
       </c>
-      <c r="E67" s="32" t="inlineStr">
+      <c r="E75" s="32" t="inlineStr">
         <is>
           <t>Nhấn icon 🔊 trên response</t>
         </is>
       </c>
-      <c r="F67" s="32" t="inlineStr">
+      <c r="F75" s="32" t="inlineStr">
         <is>
           <t>AI đọc bằng giọng nói tự nhiên</t>
         </is>
       </c>
-      <c r="G67" s="32" t="inlineStr"/>
-      <c r="H67" s="32" t="inlineStr"/>
-      <c r="I67" s="31" t="inlineStr"/>
-      <c r="J67" s="31" t="inlineStr"/>
-      <c r="K67" s="33" t="inlineStr"/>
-      <c r="L67" s="32" t="inlineStr"/>
-      <c r="M67" s="32" t="inlineStr"/>
-    </row>
-    <row r="68" ht="40" customHeight="1">
-      <c r="A68" s="31" t="n">
-        <v>64</v>
-      </c>
-      <c r="B68" s="31" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C68" s="32" t="inlineStr">
+      <c r="G75" s="32" t="inlineStr"/>
+      <c r="H75" s="32" t="inlineStr"/>
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="31" t="inlineStr"/>
+      <c r="K75" s="33" t="inlineStr"/>
+      <c r="L75" s="32" t="inlineStr"/>
+      <c r="M75" s="32" t="inlineStr"/>
+    </row>
+    <row r="76" ht="40" customHeight="1">
+      <c r="A76" s="31" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" s="31" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C76" s="32" t="inlineStr">
         <is>
           <t>Giọng nói</t>
         </is>
       </c>
-      <c r="D68" s="32" t="inlineStr">
+      <c r="D76" s="32" t="inlineStr">
         <is>
           <t>Speech-to-Text</t>
         </is>
       </c>
-      <c r="E68" s="32" t="inlineStr">
+      <c r="E76" s="32" t="inlineStr">
         <is>
           <t>Nhấn icon 🎤 → nói câu hỏi</t>
         </is>
       </c>
-      <c r="F68" s="32" t="inlineStr">
+      <c r="F76" s="32" t="inlineStr">
         <is>
           <t>Giọng nói → text chính xác</t>
         </is>
       </c>
-      <c r="G68" s="32" t="inlineStr"/>
-      <c r="H68" s="32" t="inlineStr"/>
-      <c r="I68" s="31" t="inlineStr"/>
-      <c r="J68" s="31" t="inlineStr"/>
-      <c r="K68" s="33" t="inlineStr"/>
-      <c r="L68" s="32" t="inlineStr"/>
-      <c r="M68" s="32" t="inlineStr"/>
-    </row>
-    <row r="69" ht="40" customHeight="1">
-      <c r="A69" s="31" t="n">
-        <v>65</v>
-      </c>
-      <c r="B69" s="31" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C69" s="32" t="inlineStr">
+      <c r="G76" s="32" t="inlineStr"/>
+      <c r="H76" s="32" t="inlineStr"/>
+      <c r="I76" s="31" t="inlineStr"/>
+      <c r="J76" s="31" t="inlineStr"/>
+      <c r="K76" s="33" t="inlineStr"/>
+      <c r="L76" s="32" t="inlineStr"/>
+      <c r="M76" s="32" t="inlineStr"/>
+    </row>
+    <row r="77" ht="40" customHeight="1">
+      <c r="A77" s="31" t="n">
+        <v>73</v>
+      </c>
+      <c r="B77" s="31" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C77" s="32" t="inlineStr">
         <is>
           <t>Giọng nói</t>
         </is>
       </c>
-      <c r="D69" s="32" t="inlineStr">
+      <c r="D77" s="32" t="inlineStr">
         <is>
           <t>STT tiếng Việt</t>
         </is>
       </c>
-      <c r="E69" s="32" t="inlineStr">
+      <c r="E77" s="32" t="inlineStr">
         <is>
           <t>Nói bằng tiếng Việt</t>
         </is>
       </c>
-      <c r="F69" s="32" t="inlineStr">
+      <c r="F77" s="32" t="inlineStr">
         <is>
           <t>Nhận dạng TV chính xác</t>
         </is>
       </c>
-      <c r="G69" s="32" t="inlineStr"/>
-      <c r="H69" s="32" t="inlineStr"/>
-      <c r="I69" s="31" t="inlineStr"/>
-      <c r="J69" s="31" t="inlineStr"/>
-      <c r="K69" s="33" t="inlineStr"/>
-      <c r="L69" s="32" t="inlineStr"/>
-      <c r="M69" s="32" t="inlineStr"/>
-    </row>
-    <row r="70" ht="40" customHeight="1">
-      <c r="A70" s="34" t="n">
-        <v>66</v>
-      </c>
-      <c r="B70" s="34" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C70" s="35" t="inlineStr">
+      <c r="G77" s="32" t="inlineStr"/>
+      <c r="H77" s="32" t="inlineStr"/>
+      <c r="I77" s="31" t="inlineStr"/>
+      <c r="J77" s="31" t="inlineStr"/>
+      <c r="K77" s="33" t="inlineStr"/>
+      <c r="L77" s="32" t="inlineStr"/>
+      <c r="M77" s="32" t="inlineStr"/>
+    </row>
+    <row r="78" ht="40" customHeight="1">
+      <c r="A78" s="34" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="34" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C78" s="35" t="inlineStr">
         <is>
           <t>Tìm kiếm Web</t>
         </is>
       </c>
-      <c r="D70" s="35" t="inlineStr">
+      <c r="D78" s="35" t="inlineStr">
         <is>
           <t>Web search cơ bản</t>
         </is>
       </c>
-      <c r="E70" s="35" t="inlineStr">
+      <c r="E78" s="35" t="inlineStr">
         <is>
           <t>Hỏi: "Tin tức mới nhất về AI"</t>
         </is>
       </c>
-      <c r="F70" s="35" t="inlineStr">
+      <c r="F78" s="35" t="inlineStr">
         <is>
           <t>Search web, trả lời có nguồn trích dẫn</t>
         </is>
       </c>
-      <c r="G70" s="35" t="inlineStr"/>
-      <c r="H70" s="35" t="inlineStr"/>
-      <c r="I70" s="34" t="inlineStr"/>
-      <c r="J70" s="34" t="inlineStr"/>
-      <c r="K70" s="36" t="inlineStr"/>
-      <c r="L70" s="35" t="inlineStr"/>
-      <c r="M70" s="35" t="inlineStr"/>
-    </row>
-    <row r="71" ht="40" customHeight="1">
-      <c r="A71" s="34" t="n">
-        <v>67</v>
-      </c>
-      <c r="B71" s="34" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C71" s="35" t="inlineStr">
+      <c r="G78" s="35" t="inlineStr"/>
+      <c r="H78" s="35" t="inlineStr"/>
+      <c r="I78" s="34" t="inlineStr"/>
+      <c r="J78" s="34" t="inlineStr"/>
+      <c r="K78" s="36" t="inlineStr"/>
+      <c r="L78" s="35" t="inlineStr"/>
+      <c r="M78" s="35" t="inlineStr"/>
+    </row>
+    <row r="79" ht="40" customHeight="1">
+      <c r="A79" s="34" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="34" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C79" s="35" t="inlineStr">
         <is>
           <t>Tìm kiếm Web</t>
         </is>
       </c>
-      <c r="D71" s="35" t="inlineStr">
+      <c r="D79" s="35" t="inlineStr">
         <is>
           <t>Trích dẫn nguồn web</t>
         </is>
       </c>
-      <c r="E71" s="35" t="inlineStr">
+      <c r="E79" s="35" t="inlineStr">
         <is>
           <t>Kiểm tra response có tag nguồn</t>
         </is>
       </c>
-      <c r="F71" s="35" t="inlineStr">
+      <c r="F79" s="35" t="inlineStr">
         <is>
           <t>Chip/tag website + URL</t>
         </is>
       </c>
-      <c r="G71" s="35" t="inlineStr"/>
-      <c r="H71" s="35" t="inlineStr"/>
-      <c r="I71" s="34" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr"/>
-      <c r="K71" s="36" t="inlineStr"/>
-      <c r="L71" s="35" t="inlineStr"/>
-      <c r="M71" s="35" t="inlineStr"/>
-    </row>
-    <row r="72" ht="40" customHeight="1">
-      <c r="A72" s="34" t="n">
-        <v>68</v>
-      </c>
-      <c r="B72" s="34" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C72" s="35" t="inlineStr">
+      <c r="G79" s="35" t="inlineStr"/>
+      <c r="H79" s="35" t="inlineStr"/>
+      <c r="I79" s="34" t="inlineStr"/>
+      <c r="J79" s="34" t="inlineStr"/>
+      <c r="K79" s="36" t="inlineStr"/>
+      <c r="L79" s="35" t="inlineStr"/>
+      <c r="M79" s="35" t="inlineStr"/>
+    </row>
+    <row r="80" ht="40" customHeight="1">
+      <c r="A80" s="34" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="34" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C80" s="35" t="inlineStr">
         <is>
           <t>Tìm kiếm Web</t>
         </is>
       </c>
-      <c r="D72" s="35" t="inlineStr">
+      <c r="D80" s="35" t="inlineStr">
         <is>
           <t>Search tiếng Việt</t>
         </is>
       </c>
-      <c r="E72" s="35" t="inlineStr">
+      <c r="E80" s="35" t="inlineStr">
         <is>
           <t>Hỏi: "Thời tiết Hà Nội hôm nay"</t>
         </is>
       </c>
-      <c r="F72" s="35" t="inlineStr">
+      <c r="F80" s="35" t="inlineStr">
         <is>
           <t>Tìm, trả lời TV, có nguồn</t>
         </is>
       </c>
-      <c r="G72" s="35" t="inlineStr"/>
-      <c r="H72" s="35" t="inlineStr"/>
-      <c r="I72" s="34" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr"/>
-      <c r="K72" s="36" t="inlineStr"/>
-      <c r="L72" s="35" t="inlineStr"/>
-      <c r="M72" s="35" t="inlineStr"/>
-    </row>
-    <row r="73" ht="40" customHeight="1">
-      <c r="A73" s="37" t="n">
-        <v>69</v>
-      </c>
-      <c r="B73" s="37" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C73" s="38" t="inlineStr">
+      <c r="G80" s="35" t="inlineStr"/>
+      <c r="H80" s="35" t="inlineStr"/>
+      <c r="I80" s="34" t="inlineStr"/>
+      <c r="J80" s="34" t="inlineStr"/>
+      <c r="K80" s="36" t="inlineStr"/>
+      <c r="L80" s="35" t="inlineStr"/>
+      <c r="M80" s="35" t="inlineStr"/>
+    </row>
+    <row r="81" ht="40" customHeight="1">
+      <c r="A81" s="37" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="37" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C81" s="38" t="inlineStr">
         <is>
           <t>Giao diện &amp; Cá nhân hóa</t>
         </is>
       </c>
-      <c r="D73" s="38" t="inlineStr">
+      <c r="D81" s="38" t="inlineStr">
         <is>
           <t>Dark/Light mode</t>
         </is>
       </c>
-      <c r="E73" s="38" t="inlineStr">
+      <c r="E81" s="38" t="inlineStr">
         <is>
           <t>Settings → Theme → chuyển đổi</t>
         </is>
       </c>
-      <c r="F73" s="38" t="inlineStr">
+      <c r="F81" s="38" t="inlineStr">
         <is>
           <t>Giao diện chuyển đổi mượt</t>
         </is>
       </c>
-      <c r="G73" s="38" t="inlineStr"/>
-      <c r="H73" s="38" t="inlineStr"/>
-      <c r="I73" s="37" t="inlineStr"/>
-      <c r="J73" s="37" t="inlineStr"/>
-      <c r="K73" s="39" t="inlineStr"/>
-      <c r="L73" s="38" t="inlineStr"/>
-      <c r="M73" s="38" t="inlineStr"/>
-    </row>
-    <row r="74" ht="40" customHeight="1">
-      <c r="A74" s="37" t="n">
-        <v>70</v>
-      </c>
-      <c r="B74" s="37" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C74" s="38" t="inlineStr">
+      <c r="G81" s="38" t="inlineStr"/>
+      <c r="H81" s="38" t="inlineStr"/>
+      <c r="I81" s="37" t="inlineStr"/>
+      <c r="J81" s="37" t="inlineStr"/>
+      <c r="K81" s="39" t="inlineStr"/>
+      <c r="L81" s="38" t="inlineStr"/>
+      <c r="M81" s="38" t="inlineStr"/>
+    </row>
+    <row r="82" ht="40" customHeight="1">
+      <c r="A82" s="37" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="37" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C82" s="38" t="inlineStr">
         <is>
           <t>Giao diện &amp; Cá nhân hóa</t>
         </is>
       </c>
-      <c r="D74" s="38" t="inlineStr">
+      <c r="D82" s="38" t="inlineStr">
         <is>
           <t>Ngôn ngữ</t>
         </is>
       </c>
-      <c r="E74" s="38" t="inlineStr">
+      <c r="E82" s="38" t="inlineStr">
         <is>
           <t>Settings → Language → Tiếng Việt</t>
         </is>
       </c>
-      <c r="F74" s="38" t="inlineStr">
+      <c r="F82" s="38" t="inlineStr">
         <is>
           <t>UI chuyển tiếng Việt</t>
         </is>
       </c>
-      <c r="G74" s="38" t="inlineStr"/>
-      <c r="H74" s="38" t="inlineStr"/>
-      <c r="I74" s="37" t="inlineStr"/>
-      <c r="J74" s="37" t="inlineStr"/>
-      <c r="K74" s="39" t="inlineStr"/>
-      <c r="L74" s="38" t="inlineStr"/>
-      <c r="M74" s="38" t="inlineStr"/>
-    </row>
-    <row r="75" ht="40" customHeight="1">
-      <c r="A75" s="37" t="n">
-        <v>71</v>
-      </c>
-      <c r="B75" s="37" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C75" s="38" t="inlineStr">
+      <c r="G82" s="38" t="inlineStr"/>
+      <c r="H82" s="38" t="inlineStr"/>
+      <c r="I82" s="37" t="inlineStr"/>
+      <c r="J82" s="37" t="inlineStr"/>
+      <c r="K82" s="39" t="inlineStr"/>
+      <c r="L82" s="38" t="inlineStr"/>
+      <c r="M82" s="38" t="inlineStr"/>
+    </row>
+    <row r="83" ht="40" customHeight="1">
+      <c r="A83" s="37" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="37" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C83" s="38" t="inlineStr">
         <is>
           <t>Giao diện &amp; Cá nhân hóa</t>
         </is>
       </c>
-      <c r="D75" s="38" t="inlineStr">
+      <c r="D83" s="38" t="inlineStr">
         <is>
           <t>System prompt</t>
         </is>
       </c>
-      <c r="E75" s="38" t="inlineStr">
+      <c r="E83" s="38" t="inlineStr">
         <is>
           <t>Settings → đặt system prompt</t>
         </is>
       </c>
-      <c r="F75" s="38" t="inlineStr">
+      <c r="F83" s="38" t="inlineStr">
         <is>
           <t>AI tuân theo khi chat</t>
         </is>
       </c>
-      <c r="G75" s="38" t="inlineStr"/>
-      <c r="H75" s="38" t="inlineStr"/>
-      <c r="I75" s="37" t="inlineStr"/>
-      <c r="J75" s="37" t="inlineStr"/>
-      <c r="K75" s="39" t="inlineStr"/>
-      <c r="L75" s="38" t="inlineStr"/>
-      <c r="M75" s="38" t="inlineStr"/>
-    </row>
-    <row r="76" ht="40" customHeight="1">
-      <c r="A76" s="37" t="n">
-        <v>72</v>
-      </c>
-      <c r="B76" s="37" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="C76" s="38" t="inlineStr">
+      <c r="G83" s="38" t="inlineStr"/>
+      <c r="H83" s="38" t="inlineStr"/>
+      <c r="I83" s="37" t="inlineStr"/>
+      <c r="J83" s="37" t="inlineStr"/>
+      <c r="K83" s="39" t="inlineStr"/>
+      <c r="L83" s="38" t="inlineStr"/>
+      <c r="M83" s="38" t="inlineStr"/>
+    </row>
+    <row r="84" ht="40" customHeight="1">
+      <c r="A84" s="37" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="37" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="C84" s="38" t="inlineStr">
         <is>
           <t>Giao diện &amp; Cá nhân hóa</t>
         </is>
       </c>
-      <c r="D76" s="38" t="inlineStr">
+      <c r="D84" s="38" t="inlineStr">
         <is>
           <t>Responsive mobile</t>
         </is>
       </c>
-      <c r="E76" s="38" t="inlineStr">
+      <c r="E84" s="38" t="inlineStr">
         <is>
           <t>Mở trên điện thoại</t>
         </is>
       </c>
-      <c r="F76" s="38" t="inlineStr">
+      <c r="F84" s="38" t="inlineStr">
         <is>
           <t>Hiển thị tốt, không vỡ layout</t>
         </is>
       </c>
-      <c r="G76" s="38" t="inlineStr"/>
-      <c r="H76" s="38" t="inlineStr"/>
-      <c r="I76" s="37" t="inlineStr"/>
-      <c r="J76" s="37" t="inlineStr"/>
-      <c r="K76" s="39" t="inlineStr"/>
-      <c r="L76" s="38" t="inlineStr"/>
-      <c r="M76" s="38" t="inlineStr"/>
-    </row>
-    <row r="77" ht="28" customHeight="1">
-      <c r="A77" s="40" t="inlineStr">
+      <c r="G84" s="38" t="inlineStr"/>
+      <c r="H84" s="38" t="inlineStr"/>
+      <c r="I84" s="37" t="inlineStr"/>
+      <c r="J84" s="37" t="inlineStr"/>
+      <c r="K84" s="39" t="inlineStr"/>
+      <c r="L84" s="38" t="inlineStr"/>
+      <c r="M84" s="38" t="inlineStr"/>
+    </row>
+    <row r="85" ht="28" customHeight="1">
+      <c r="A85" s="40" t="inlineStr">
         <is>
           <t>PHẦN B: TÍNH NĂNG QUẢN TRỊ (ADMIN)</t>
         </is>
       </c>
-      <c r="B77" s="41" t="n"/>
-      <c r="C77" s="41" t="n"/>
-      <c r="D77" s="41" t="n"/>
-      <c r="E77" s="41" t="n"/>
-      <c r="F77" s="41" t="n"/>
-      <c r="G77" s="41" t="n"/>
-      <c r="H77" s="41" t="n"/>
-      <c r="I77" s="41" t="n"/>
-      <c r="J77" s="41" t="n"/>
-      <c r="K77" s="42" t="n"/>
-      <c r="L77" s="41" t="n"/>
-      <c r="M77" s="41" t="n"/>
-    </row>
-    <row r="78" ht="40" customHeight="1">
-      <c r="A78" s="43" t="n">
-        <v>73</v>
-      </c>
-      <c r="B78" s="43" t="inlineStr">
+      <c r="B85" s="41" t="n"/>
+      <c r="C85" s="41" t="n"/>
+      <c r="D85" s="41" t="n"/>
+      <c r="E85" s="41" t="n"/>
+      <c r="F85" s="41" t="n"/>
+      <c r="G85" s="41" t="n"/>
+      <c r="H85" s="41" t="n"/>
+      <c r="I85" s="41" t="n"/>
+      <c r="J85" s="41" t="n"/>
+      <c r="K85" s="42" t="n"/>
+      <c r="L85" s="41" t="n"/>
+      <c r="M85" s="41" t="n"/>
+    </row>
+    <row r="86" ht="40" customHeight="1">
+      <c r="A86" s="43" t="n">
+        <v>81</v>
+      </c>
+      <c r="B86" s="43" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C78" s="44" t="inlineStr">
+      <c r="C86" s="44" t="inlineStr">
         <is>
           <t>Quản lý người dùng</t>
         </is>
       </c>
-      <c r="D78" s="44" t="inlineStr">
+      <c r="D86" s="44" t="inlineStr">
         <is>
           <t>Xem danh sách user</t>
         </is>
       </c>
-      <c r="E78" s="44" t="inlineStr">
+      <c r="E86" s="44" t="inlineStr">
         <is>
           <t>Admin Panel → Users</t>
         </is>
       </c>
-      <c r="F78" s="44" t="inlineStr">
+      <c r="F86" s="44" t="inlineStr">
         <is>
           <t>Hiển thị đầy đủ, role, trạng thái</t>
         </is>
       </c>
-      <c r="G78" s="44" t="inlineStr"/>
-      <c r="H78" s="44" t="inlineStr"/>
-      <c r="I78" s="43" t="inlineStr"/>
-      <c r="J78" s="43" t="inlineStr"/>
-      <c r="K78" s="45" t="inlineStr"/>
-      <c r="L78" s="44" t="inlineStr"/>
-      <c r="M78" s="44" t="inlineStr"/>
-    </row>
-    <row r="79" ht="40" customHeight="1">
-      <c r="A79" s="43" t="n">
-        <v>74</v>
-      </c>
-      <c r="B79" s="43" t="inlineStr">
+      <c r="G86" s="44" t="inlineStr"/>
+      <c r="H86" s="44" t="inlineStr"/>
+      <c r="I86" s="43" t="inlineStr"/>
+      <c r="J86" s="43" t="inlineStr"/>
+      <c r="K86" s="45" t="inlineStr"/>
+      <c r="L86" s="44" t="inlineStr"/>
+      <c r="M86" s="44" t="inlineStr"/>
+    </row>
+    <row r="87" ht="40" customHeight="1">
+      <c r="A87" s="43" t="n">
+        <v>82</v>
+      </c>
+      <c r="B87" s="43" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C79" s="44" t="inlineStr">
+      <c r="C87" s="44" t="inlineStr">
         <is>
           <t>Quản lý người dùng</t>
         </is>
       </c>
-      <c r="D79" s="44" t="inlineStr">
+      <c r="D87" s="44" t="inlineStr">
         <is>
           <t>Tạo user mới</t>
         </is>
       </c>
-      <c r="E79" s="44" t="inlineStr">
+      <c r="E87" s="44" t="inlineStr">
         <is>
           <t>Tạo account / đăng ký</t>
         </is>
       </c>
-      <c r="F79" s="44" t="inlineStr">
+      <c r="F87" s="44" t="inlineStr">
         <is>
           <t>Account tạo, trạng thái Pending</t>
         </is>
       </c>
-      <c r="G79" s="44" t="inlineStr"/>
-      <c r="H79" s="44" t="inlineStr"/>
-      <c r="I79" s="43" t="inlineStr"/>
-      <c r="J79" s="43" t="inlineStr"/>
-      <c r="K79" s="45" t="inlineStr"/>
-      <c r="L79" s="44" t="inlineStr"/>
-      <c r="M79" s="44" t="inlineStr"/>
-    </row>
-    <row r="80" ht="40" customHeight="1">
-      <c r="A80" s="43" t="n">
-        <v>75</v>
-      </c>
-      <c r="B80" s="43" t="inlineStr">
+      <c r="G87" s="44" t="inlineStr"/>
+      <c r="H87" s="44" t="inlineStr"/>
+      <c r="I87" s="43" t="inlineStr"/>
+      <c r="J87" s="43" t="inlineStr"/>
+      <c r="K87" s="45" t="inlineStr"/>
+      <c r="L87" s="44" t="inlineStr"/>
+      <c r="M87" s="44" t="inlineStr"/>
+    </row>
+    <row r="88" ht="40" customHeight="1">
+      <c r="A88" s="43" t="n">
+        <v>83</v>
+      </c>
+      <c r="B88" s="43" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C80" s="44" t="inlineStr">
+      <c r="C88" s="44" t="inlineStr">
         <is>
           <t>Quản lý người dùng</t>
         </is>
       </c>
-      <c r="D80" s="44" t="inlineStr">
+      <c r="D88" s="44" t="inlineStr">
         <is>
           <t>Duyệt user</t>
         </is>
       </c>
-      <c r="E80" s="44" t="inlineStr">
+      <c r="E88" s="44" t="inlineStr">
         <is>
           <t>Approve user pending</t>
         </is>
       </c>
-      <c r="F80" s="44" t="inlineStr">
+      <c r="F88" s="44" t="inlineStr">
         <is>
           <t>User Active, login được</t>
         </is>
       </c>
-      <c r="G80" s="44" t="inlineStr"/>
-      <c r="H80" s="44" t="inlineStr"/>
-      <c r="I80" s="43" t="inlineStr"/>
-      <c r="J80" s="43" t="inlineStr"/>
-      <c r="K80" s="45" t="inlineStr"/>
-      <c r="L80" s="44" t="inlineStr"/>
-      <c r="M80" s="44" t="inlineStr"/>
-    </row>
-    <row r="81" ht="40" customHeight="1">
-      <c r="A81" s="43" t="n">
-        <v>76</v>
-      </c>
-      <c r="B81" s="43" t="inlineStr">
+      <c r="G88" s="44" t="inlineStr"/>
+      <c r="H88" s="44" t="inlineStr"/>
+      <c r="I88" s="43" t="inlineStr"/>
+      <c r="J88" s="43" t="inlineStr"/>
+      <c r="K88" s="45" t="inlineStr"/>
+      <c r="L88" s="44" t="inlineStr"/>
+      <c r="M88" s="44" t="inlineStr"/>
+    </row>
+    <row r="89" ht="40" customHeight="1">
+      <c r="A89" s="43" t="n">
+        <v>84</v>
+      </c>
+      <c r="B89" s="43" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C81" s="44" t="inlineStr">
+      <c r="C89" s="44" t="inlineStr">
         <is>
           <t>Quản lý người dùng</t>
         </is>
       </c>
-      <c r="D81" s="44" t="inlineStr">
+      <c r="D89" s="44" t="inlineStr">
         <is>
           <t>Đổi role</t>
         </is>
       </c>
-      <c r="E81" s="44" t="inlineStr">
+      <c r="E89" s="44" t="inlineStr">
         <is>
           <t>User → Admin hoặc ngược lại</t>
         </is>
       </c>
-      <c r="F81" s="44" t="inlineStr">
+      <c r="F89" s="44" t="inlineStr">
         <is>
           <t>Role + quyền thay đổi</t>
         </is>
       </c>
-      <c r="G81" s="44" t="inlineStr"/>
-      <c r="H81" s="44" t="inlineStr"/>
-      <c r="I81" s="43" t="inlineStr"/>
-      <c r="J81" s="43" t="inlineStr"/>
-      <c r="K81" s="45" t="inlineStr"/>
-      <c r="L81" s="44" t="inlineStr"/>
-      <c r="M81" s="44" t="inlineStr"/>
-    </row>
-    <row r="82" ht="40" customHeight="1">
-      <c r="A82" s="43" t="n">
-        <v>77</v>
-      </c>
-      <c r="B82" s="43" t="inlineStr">
+      <c r="G89" s="44" t="inlineStr"/>
+      <c r="H89" s="44" t="inlineStr"/>
+      <c r="I89" s="43" t="inlineStr"/>
+      <c r="J89" s="43" t="inlineStr"/>
+      <c r="K89" s="45" t="inlineStr"/>
+      <c r="L89" s="44" t="inlineStr"/>
+      <c r="M89" s="44" t="inlineStr"/>
+    </row>
+    <row r="90" ht="40" customHeight="1">
+      <c r="A90" s="43" t="n">
+        <v>85</v>
+      </c>
+      <c r="B90" s="43" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C82" s="44" t="inlineStr">
+      <c r="C90" s="44" t="inlineStr">
         <is>
           <t>Quản lý người dùng</t>
         </is>
       </c>
-      <c r="D82" s="44" t="inlineStr">
+      <c r="D90" s="44" t="inlineStr">
         <is>
           <t>Xóa user</t>
         </is>
       </c>
-      <c r="E82" s="44" t="inlineStr">
+      <c r="E90" s="44" t="inlineStr">
         <is>
           <t>Xóa 1 user account</t>
         </is>
       </c>
-      <c r="F82" s="44" t="inlineStr">
+      <c r="F90" s="44" t="inlineStr">
         <is>
           <t>User bị xóa, không login</t>
         </is>
       </c>
-      <c r="G82" s="44" t="inlineStr"/>
-      <c r="H82" s="44" t="inlineStr"/>
-      <c r="I82" s="43" t="inlineStr"/>
-      <c r="J82" s="43" t="inlineStr"/>
-      <c r="K82" s="45" t="inlineStr"/>
-      <c r="L82" s="44" t="inlineStr"/>
-      <c r="M82" s="44" t="inlineStr"/>
-    </row>
-    <row r="83" ht="40" customHeight="1">
-      <c r="A83" s="43" t="n">
-        <v>78</v>
-      </c>
-      <c r="B83" s="43" t="inlineStr">
+      <c r="G90" s="44" t="inlineStr"/>
+      <c r="H90" s="44" t="inlineStr"/>
+      <c r="I90" s="43" t="inlineStr"/>
+      <c r="J90" s="43" t="inlineStr"/>
+      <c r="K90" s="45" t="inlineStr"/>
+      <c r="L90" s="44" t="inlineStr"/>
+      <c r="M90" s="44" t="inlineStr"/>
+    </row>
+    <row r="91" ht="40" customHeight="1">
+      <c r="A91" s="43" t="n">
+        <v>86</v>
+      </c>
+      <c r="B91" s="43" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C83" s="44" t="inlineStr">
+      <c r="C91" s="44" t="inlineStr">
         <is>
           <t>Quản lý người dùng</t>
         </is>
       </c>
-      <c r="D83" s="44" t="inlineStr">
+      <c r="D91" s="44" t="inlineStr">
         <is>
           <t>Reset password</t>
         </is>
       </c>
-      <c r="E83" s="44" t="inlineStr">
+      <c r="E91" s="44" t="inlineStr">
         <is>
           <t>Reset password cho user</t>
         </is>
       </c>
-      <c r="F83" s="44" t="inlineStr">
+      <c r="F91" s="44" t="inlineStr">
         <is>
           <t>Password mới hoạt động</t>
         </is>
       </c>
-      <c r="G83" s="44" t="inlineStr"/>
-      <c r="H83" s="44" t="inlineStr"/>
-      <c r="I83" s="43" t="inlineStr"/>
-      <c r="J83" s="43" t="inlineStr"/>
-      <c r="K83" s="45" t="inlineStr"/>
-      <c r="L83" s="44" t="inlineStr"/>
-      <c r="M83" s="44" t="inlineStr"/>
-    </row>
-    <row r="84" ht="40" customHeight="1">
-      <c r="A84" s="46" t="n">
-        <v>79</v>
-      </c>
-      <c r="B84" s="46" t="inlineStr">
+      <c r="G91" s="44" t="inlineStr"/>
+      <c r="H91" s="44" t="inlineStr"/>
+      <c r="I91" s="43" t="inlineStr"/>
+      <c r="J91" s="43" t="inlineStr"/>
+      <c r="K91" s="45" t="inlineStr"/>
+      <c r="L91" s="44" t="inlineStr"/>
+      <c r="M91" s="44" t="inlineStr"/>
+    </row>
+    <row r="92" ht="40" customHeight="1">
+      <c r="A92" s="46" t="n">
+        <v>87</v>
+      </c>
+      <c r="B92" s="46" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C84" s="47" t="inlineStr">
+      <c r="C92" s="47" t="inlineStr">
         <is>
           <t>Quản lý Model</t>
         </is>
       </c>
-      <c r="D84" s="47" t="inlineStr">
+      <c r="D92" s="47" t="inlineStr">
         <is>
           <t>Bật/tắt model</t>
         </is>
       </c>
-      <c r="E84" s="47" t="inlineStr">
+      <c r="E92" s="47" t="inlineStr">
         <is>
           <t>Admin → Models → Disable</t>
         </is>
       </c>
-      <c r="F84" s="47" t="inlineStr">
+      <c r="F92" s="47" t="inlineStr">
         <is>
           <t>User không thấy model disabled</t>
         </is>
       </c>
-      <c r="G84" s="47" t="inlineStr"/>
-      <c r="H84" s="47" t="inlineStr"/>
-      <c r="I84" s="46" t="inlineStr"/>
-      <c r="J84" s="46" t="inlineStr"/>
-      <c r="K84" s="48" t="inlineStr"/>
-      <c r="L84" s="47" t="inlineStr"/>
-      <c r="M84" s="47" t="inlineStr"/>
-    </row>
-    <row r="85" ht="40" customHeight="1">
-      <c r="A85" s="46" t="n">
-        <v>80</v>
-      </c>
-      <c r="B85" s="46" t="inlineStr">
+      <c r="G92" s="47" t="inlineStr"/>
+      <c r="H92" s="47" t="inlineStr"/>
+      <c r="I92" s="46" t="inlineStr"/>
+      <c r="J92" s="46" t="inlineStr"/>
+      <c r="K92" s="48" t="inlineStr"/>
+      <c r="L92" s="47" t="inlineStr"/>
+      <c r="M92" s="47" t="inlineStr"/>
+    </row>
+    <row r="93" ht="40" customHeight="1">
+      <c r="A93" s="46" t="n">
+        <v>88</v>
+      </c>
+      <c r="B93" s="46" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C85" s="47" t="inlineStr">
+      <c r="C93" s="47" t="inlineStr">
         <is>
           <t>Quản lý Model</t>
         </is>
       </c>
-      <c r="D85" s="47" t="inlineStr">
+      <c r="D93" s="47" t="inlineStr">
         <is>
           <t>Cấu hình params</t>
         </is>
       </c>
-      <c r="E85" s="47" t="inlineStr">
+      <c r="E93" s="47" t="inlineStr">
         <is>
           <t>Set temperature, max_tokens</t>
         </is>
       </c>
-      <c r="F85" s="47" t="inlineStr">
+      <c r="F93" s="47" t="inlineStr">
         <is>
           <t>Params áp dụng khi chat</t>
         </is>
       </c>
-      <c r="G85" s="47" t="inlineStr"/>
-      <c r="H85" s="47" t="inlineStr"/>
-      <c r="I85" s="46" t="inlineStr"/>
-      <c r="J85" s="46" t="inlineStr"/>
-      <c r="K85" s="48" t="inlineStr"/>
-      <c r="L85" s="47" t="inlineStr"/>
-      <c r="M85" s="47" t="inlineStr"/>
-    </row>
-    <row r="86" ht="40" customHeight="1">
-      <c r="A86" s="46" t="n">
-        <v>81</v>
-      </c>
-      <c r="B86" s="46" t="inlineStr">
+      <c r="G93" s="47" t="inlineStr"/>
+      <c r="H93" s="47" t="inlineStr"/>
+      <c r="I93" s="46" t="inlineStr"/>
+      <c r="J93" s="46" t="inlineStr"/>
+      <c r="K93" s="48" t="inlineStr"/>
+      <c r="L93" s="47" t="inlineStr"/>
+      <c r="M93" s="47" t="inlineStr"/>
+    </row>
+    <row r="94" ht="40" customHeight="1">
+      <c r="A94" s="46" t="n">
+        <v>89</v>
+      </c>
+      <c r="B94" s="46" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C86" s="47" t="inlineStr">
+      <c r="C94" s="47" t="inlineStr">
         <is>
           <t>Quản lý Model</t>
         </is>
       </c>
-      <c r="D86" s="47" t="inlineStr">
+      <c r="D94" s="47" t="inlineStr">
         <is>
           <t>Gán Knowledge</t>
         </is>
       </c>
-      <c r="E86" s="47" t="inlineStr">
+      <c r="E94" s="47" t="inlineStr">
         <is>
           <t>Gán Knowledge mặc định cho model</t>
         </is>
       </c>
-      <c r="F86" s="47" t="inlineStr">
+      <c r="F94" s="47" t="inlineStr">
         <is>
           <t>Model tự động dùng Knowledge</t>
         </is>
       </c>
-      <c r="G86" s="47" t="inlineStr"/>
-      <c r="H86" s="47" t="inlineStr"/>
-      <c r="I86" s="46" t="inlineStr"/>
-      <c r="J86" s="46" t="inlineStr"/>
-      <c r="K86" s="48" t="inlineStr"/>
-      <c r="L86" s="47" t="inlineStr"/>
-      <c r="M86" s="47" t="inlineStr"/>
-    </row>
-    <row r="87" ht="40" customHeight="1">
-      <c r="A87" s="46" t="n">
-        <v>82</v>
-      </c>
-      <c r="B87" s="46" t="inlineStr">
+      <c r="G94" s="47" t="inlineStr"/>
+      <c r="H94" s="47" t="inlineStr"/>
+      <c r="I94" s="46" t="inlineStr"/>
+      <c r="J94" s="46" t="inlineStr"/>
+      <c r="K94" s="48" t="inlineStr"/>
+      <c r="L94" s="47" t="inlineStr"/>
+      <c r="M94" s="47" t="inlineStr"/>
+    </row>
+    <row r="95" ht="40" customHeight="1">
+      <c r="A95" s="46" t="n">
+        <v>90</v>
+      </c>
+      <c r="B95" s="46" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C87" s="47" t="inlineStr">
+      <c r="C95" s="47" t="inlineStr">
         <is>
           <t>Quản lý Model</t>
         </is>
       </c>
-      <c r="D87" s="47" t="inlineStr">
+      <c r="D95" s="47" t="inlineStr">
         <is>
           <t>Access control</t>
         </is>
       </c>
-      <c r="E87" s="47" t="inlineStr">
+      <c r="E95" s="47" t="inlineStr">
         <is>
           <t>Giới hạn model cho user cụ thể</t>
         </is>
       </c>
-      <c r="F87" s="47" t="inlineStr">
+      <c r="F95" s="47" t="inlineStr">
         <is>
           <t>Chỉ user được phép mới thấy</t>
         </is>
       </c>
-      <c r="G87" s="47" t="inlineStr"/>
-      <c r="H87" s="47" t="inlineStr"/>
-      <c r="I87" s="46" t="inlineStr"/>
-      <c r="J87" s="46" t="inlineStr"/>
-      <c r="K87" s="48" t="inlineStr"/>
-      <c r="L87" s="47" t="inlineStr"/>
-      <c r="M87" s="47" t="inlineStr"/>
-    </row>
-    <row r="88" ht="40" customHeight="1">
-      <c r="A88" s="49" t="n">
-        <v>83</v>
-      </c>
-      <c r="B88" s="49" t="inlineStr">
+      <c r="G95" s="47" t="inlineStr"/>
+      <c r="H95" s="47" t="inlineStr"/>
+      <c r="I95" s="46" t="inlineStr"/>
+      <c r="J95" s="46" t="inlineStr"/>
+      <c r="K95" s="48" t="inlineStr"/>
+      <c r="L95" s="47" t="inlineStr"/>
+      <c r="M95" s="47" t="inlineStr"/>
+    </row>
+    <row r="96" ht="40" customHeight="1">
+      <c r="A96" s="49" t="n">
+        <v>91</v>
+      </c>
+      <c r="B96" s="49" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C88" s="50" t="inlineStr">
+      <c r="C96" s="50" t="inlineStr">
         <is>
           <t>Dashboard &amp; Giám sát</t>
         </is>
       </c>
-      <c r="D88" s="50" t="inlineStr">
+      <c r="D96" s="50" t="inlineStr">
         <is>
           <t>Dashboard tổng quan</t>
         </is>
       </c>
-      <c r="E88" s="50" t="inlineStr">
+      <c r="E96" s="50" t="inlineStr">
         <is>
           <t>Truy cập Dashboard middleware</t>
         </is>
       </c>
-      <c r="F88" s="50" t="inlineStr">
+      <c r="F96" s="50" t="inlineStr">
         <is>
           <t>Hiển thị tổng chi phí, request, top users</t>
         </is>
       </c>
-      <c r="G88" s="50" t="inlineStr"/>
-      <c r="H88" s="50" t="inlineStr"/>
-      <c r="I88" s="49" t="inlineStr"/>
-      <c r="J88" s="49" t="inlineStr"/>
-      <c r="K88" s="51" t="inlineStr"/>
-      <c r="L88" s="50" t="inlineStr"/>
-      <c r="M88" s="50" t="inlineStr"/>
-    </row>
-    <row r="89" ht="40" customHeight="1">
-      <c r="A89" s="49" t="n">
-        <v>84</v>
-      </c>
-      <c r="B89" s="49" t="inlineStr">
+      <c r="G96" s="50" t="inlineStr"/>
+      <c r="H96" s="50" t="inlineStr"/>
+      <c r="I96" s="49" t="inlineStr"/>
+      <c r="J96" s="49" t="inlineStr"/>
+      <c r="K96" s="51" t="inlineStr"/>
+      <c r="L96" s="50" t="inlineStr"/>
+      <c r="M96" s="50" t="inlineStr"/>
+    </row>
+    <row r="97" ht="40" customHeight="1">
+      <c r="A97" s="49" t="n">
+        <v>92</v>
+      </c>
+      <c r="B97" s="49" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C89" s="50" t="inlineStr">
+      <c r="C97" s="50" t="inlineStr">
         <is>
           <t>Dashboard &amp; Giám sát</t>
         </is>
       </c>
-      <c r="D89" s="50" t="inlineStr">
+      <c r="D97" s="50" t="inlineStr">
         <is>
           <t>Log requests</t>
         </is>
       </c>
-      <c r="E89" s="50" t="inlineStr">
+      <c r="E97" s="50" t="inlineStr">
         <is>
           <t>Xem log chi tiết API request</t>
         </is>
       </c>
-      <c r="F89" s="50" t="inlineStr">
+      <c r="F97" s="50" t="inlineStr">
         <is>
           <t>User, model, tokens, cost, timestamp</t>
         </is>
       </c>
-      <c r="G89" s="50" t="inlineStr"/>
-      <c r="H89" s="50" t="inlineStr"/>
-      <c r="I89" s="49" t="inlineStr"/>
-      <c r="J89" s="49" t="inlineStr"/>
-      <c r="K89" s="51" t="inlineStr"/>
-      <c r="L89" s="50" t="inlineStr"/>
-      <c r="M89" s="50" t="inlineStr"/>
-    </row>
-    <row r="90" ht="40" customHeight="1">
-      <c r="A90" s="49" t="n">
-        <v>85</v>
-      </c>
-      <c r="B90" s="49" t="inlineStr">
+      <c r="G97" s="50" t="inlineStr"/>
+      <c r="H97" s="50" t="inlineStr"/>
+      <c r="I97" s="49" t="inlineStr"/>
+      <c r="J97" s="49" t="inlineStr"/>
+      <c r="K97" s="51" t="inlineStr"/>
+      <c r="L97" s="50" t="inlineStr"/>
+      <c r="M97" s="50" t="inlineStr"/>
+    </row>
+    <row r="98" ht="40" customHeight="1">
+      <c r="A98" s="49" t="n">
+        <v>93</v>
+      </c>
+      <c r="B98" s="49" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C90" s="50" t="inlineStr">
+      <c r="C98" s="50" t="inlineStr">
         <is>
           <t>Dashboard &amp; Giám sát</t>
         </is>
       </c>
-      <c r="D90" s="50" t="inlineStr">
+      <c r="D98" s="50" t="inlineStr">
         <is>
           <t>Báo cáo theo user</t>
         </is>
       </c>
-      <c r="E90" s="50" t="inlineStr">
+      <c r="E98" s="50" t="inlineStr">
         <is>
           <t>Lọc chi phí theo user</t>
         </is>
       </c>
-      <c r="F90" s="50" t="inlineStr">
+      <c r="F98" s="50" t="inlineStr">
         <is>
           <t>Dữ liệu chính xác</t>
         </is>
       </c>
-      <c r="G90" s="50" t="inlineStr"/>
-      <c r="H90" s="50" t="inlineStr"/>
-      <c r="I90" s="49" t="inlineStr"/>
-      <c r="J90" s="49" t="inlineStr"/>
-      <c r="K90" s="51" t="inlineStr"/>
-      <c r="L90" s="50" t="inlineStr"/>
-      <c r="M90" s="50" t="inlineStr"/>
-    </row>
-    <row r="91" ht="40" customHeight="1">
-      <c r="A91" s="49" t="n">
-        <v>86</v>
-      </c>
-      <c r="B91" s="49" t="inlineStr">
+      <c r="G98" s="50" t="inlineStr"/>
+      <c r="H98" s="50" t="inlineStr"/>
+      <c r="I98" s="49" t="inlineStr"/>
+      <c r="J98" s="49" t="inlineStr"/>
+      <c r="K98" s="51" t="inlineStr"/>
+      <c r="L98" s="50" t="inlineStr"/>
+      <c r="M98" s="50" t="inlineStr"/>
+    </row>
+    <row r="99" ht="40" customHeight="1">
+      <c r="A99" s="49" t="n">
+        <v>94</v>
+      </c>
+      <c r="B99" s="49" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C91" s="50" t="inlineStr">
+      <c r="C99" s="50" t="inlineStr">
         <is>
           <t>Dashboard &amp; Giám sát</t>
         </is>
       </c>
-      <c r="D91" s="50" t="inlineStr">
+      <c r="D99" s="50" t="inlineStr">
         <is>
           <t>Báo cáo theo model</t>
         </is>
       </c>
-      <c r="E91" s="50" t="inlineStr">
+      <c r="E99" s="50" t="inlineStr">
         <is>
           <t>Lọc chi phí theo model</t>
         </is>
       </c>
-      <c r="F91" s="50" t="inlineStr">
+      <c r="F99" s="50" t="inlineStr">
         <is>
           <t>Dữ liệu chính xác</t>
         </is>
       </c>
-      <c r="G91" s="50" t="inlineStr"/>
-      <c r="H91" s="50" t="inlineStr"/>
-      <c r="I91" s="49" t="inlineStr"/>
-      <c r="J91" s="49" t="inlineStr"/>
-      <c r="K91" s="51" t="inlineStr"/>
-      <c r="L91" s="50" t="inlineStr"/>
-      <c r="M91" s="50" t="inlineStr"/>
-    </row>
-    <row r="92" ht="40" customHeight="1">
-      <c r="A92" s="49" t="n">
-        <v>87</v>
-      </c>
-      <c r="B92" s="49" t="inlineStr">
+      <c r="G99" s="50" t="inlineStr"/>
+      <c r="H99" s="50" t="inlineStr"/>
+      <c r="I99" s="49" t="inlineStr"/>
+      <c r="J99" s="49" t="inlineStr"/>
+      <c r="K99" s="51" t="inlineStr"/>
+      <c r="L99" s="50" t="inlineStr"/>
+      <c r="M99" s="50" t="inlineStr"/>
+    </row>
+    <row r="100" ht="40" customHeight="1">
+      <c r="A100" s="49" t="n">
+        <v>95</v>
+      </c>
+      <c r="B100" s="49" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C92" s="50" t="inlineStr">
+      <c r="C100" s="50" t="inlineStr">
         <is>
           <t>Dashboard &amp; Giám sát</t>
         </is>
       </c>
-      <c r="D92" s="50" t="inlineStr">
+      <c r="D100" s="50" t="inlineStr">
         <is>
           <t>Báo cáo theo thời gian</t>
         </is>
       </c>
-      <c r="E92" s="50" t="inlineStr">
+      <c r="E100" s="50" t="inlineStr">
         <is>
           <t>Lọc theo khoảng thời gian</t>
         </is>
       </c>
-      <c r="F92" s="50" t="inlineStr">
+      <c r="F100" s="50" t="inlineStr">
         <is>
           <t>Dữ liệu đúng khoảng chọn</t>
         </is>
       </c>
-      <c r="G92" s="50" t="inlineStr"/>
-      <c r="H92" s="50" t="inlineStr"/>
-      <c r="I92" s="49" t="inlineStr"/>
-      <c r="J92" s="49" t="inlineStr"/>
-      <c r="K92" s="51" t="inlineStr"/>
-      <c r="L92" s="50" t="inlineStr"/>
-      <c r="M92" s="50" t="inlineStr"/>
-    </row>
-    <row r="93" ht="40" customHeight="1">
-      <c r="A93" s="52" t="n">
-        <v>88</v>
-      </c>
-      <c r="B93" s="52" t="inlineStr">
+      <c r="G100" s="50" t="inlineStr"/>
+      <c r="H100" s="50" t="inlineStr"/>
+      <c r="I100" s="49" t="inlineStr"/>
+      <c r="J100" s="49" t="inlineStr"/>
+      <c r="K100" s="51" t="inlineStr"/>
+      <c r="L100" s="50" t="inlineStr"/>
+      <c r="M100" s="50" t="inlineStr"/>
+    </row>
+    <row r="101" ht="40" customHeight="1">
+      <c r="A101" s="52" t="n">
+        <v>96</v>
+      </c>
+      <c r="B101" s="52" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C93" s="53" t="inlineStr">
+      <c r="C101" s="53" t="inlineStr">
         <is>
           <t>Quota &amp; Chi phí</t>
         </is>
       </c>
-      <c r="D93" s="53" t="inlineStr">
+      <c r="D101" s="53" t="inlineStr">
         <is>
           <t>Set quota user</t>
         </is>
       </c>
-      <c r="E93" s="53" t="inlineStr">
+      <c r="E101" s="53" t="inlineStr">
         <is>
           <t>Dashboard → set limit_cost_usd</t>
         </is>
       </c>
-      <c r="F93" s="53" t="inlineStr">
+      <c r="F101" s="53" t="inlineStr">
         <is>
           <t>Quota lưu thành công</t>
         </is>
       </c>
-      <c r="G93" s="53" t="inlineStr"/>
-      <c r="H93" s="53" t="inlineStr"/>
-      <c r="I93" s="52" t="inlineStr"/>
-      <c r="J93" s="52" t="inlineStr"/>
-      <c r="K93" s="54" t="inlineStr"/>
-      <c r="L93" s="53" t="inlineStr"/>
-      <c r="M93" s="53" t="inlineStr"/>
-    </row>
-    <row r="94" ht="40" customHeight="1">
-      <c r="A94" s="52" t="n">
-        <v>89</v>
-      </c>
-      <c r="B94" s="52" t="inlineStr">
+      <c r="G101" s="53" t="inlineStr"/>
+      <c r="H101" s="53" t="inlineStr"/>
+      <c r="I101" s="52" t="inlineStr"/>
+      <c r="J101" s="52" t="inlineStr"/>
+      <c r="K101" s="54" t="inlineStr"/>
+      <c r="L101" s="53" t="inlineStr"/>
+      <c r="M101" s="53" t="inlineStr"/>
+    </row>
+    <row r="102" ht="40" customHeight="1">
+      <c r="A102" s="52" t="n">
+        <v>97</v>
+      </c>
+      <c r="B102" s="52" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C94" s="53" t="inlineStr">
+      <c r="C102" s="53" t="inlineStr">
         <is>
           <t>Quota &amp; Chi phí</t>
         </is>
       </c>
-      <c r="D94" s="53" t="inlineStr">
+      <c r="D102" s="53" t="inlineStr">
         <is>
           <t>Cảnh báo quota</t>
         </is>
       </c>
-      <c r="E94" s="53" t="inlineStr">
+      <c r="E102" s="53" t="inlineStr">
         <is>
           <t>User chat gần hết quota</t>
         </is>
       </c>
-      <c r="F94" s="53" t="inlineStr">
+      <c r="F102" s="53" t="inlineStr">
         <is>
           <t>Hiển thị cảnh báo</t>
         </is>
       </c>
-      <c r="G94" s="53" t="inlineStr"/>
-      <c r="H94" s="53" t="inlineStr"/>
-      <c r="I94" s="52" t="inlineStr"/>
-      <c r="J94" s="52" t="inlineStr"/>
-      <c r="K94" s="54" t="inlineStr"/>
-      <c r="L94" s="53" t="inlineStr"/>
-      <c r="M94" s="53" t="inlineStr"/>
-    </row>
-    <row r="95" ht="40" customHeight="1">
-      <c r="A95" s="52" t="n">
-        <v>90</v>
-      </c>
-      <c r="B95" s="52" t="inlineStr">
+      <c r="G102" s="53" t="inlineStr"/>
+      <c r="H102" s="53" t="inlineStr"/>
+      <c r="I102" s="52" t="inlineStr"/>
+      <c r="J102" s="52" t="inlineStr"/>
+      <c r="K102" s="54" t="inlineStr"/>
+      <c r="L102" s="53" t="inlineStr"/>
+      <c r="M102" s="53" t="inlineStr"/>
+    </row>
+    <row r="103" ht="40" customHeight="1">
+      <c r="A103" s="52" t="n">
+        <v>98</v>
+      </c>
+      <c r="B103" s="52" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C95" s="53" t="inlineStr">
+      <c r="C103" s="53" t="inlineStr">
         <is>
           <t>Quota &amp; Chi phí</t>
         </is>
       </c>
-      <c r="D95" s="53" t="inlineStr">
+      <c r="D103" s="53" t="inlineStr">
         <is>
           <t>Chặn khi hết</t>
         </is>
       </c>
-      <c r="E95" s="53" t="inlineStr">
+      <c r="E103" s="53" t="inlineStr">
         <is>
           <t>User vượt quota → chat tiếp</t>
         </is>
       </c>
-      <c r="F95" s="53" t="inlineStr">
+      <c r="F103" s="53" t="inlineStr">
         <is>
           <t>Từ chối, báo HTTP 429</t>
         </is>
       </c>
-      <c r="G95" s="53" t="inlineStr"/>
-      <c r="H95" s="53" t="inlineStr"/>
-      <c r="I95" s="52" t="inlineStr"/>
-      <c r="J95" s="52" t="inlineStr"/>
-      <c r="K95" s="54" t="inlineStr"/>
-      <c r="L95" s="53" t="inlineStr"/>
-      <c r="M95" s="53" t="inlineStr"/>
-    </row>
-    <row r="96" ht="40" customHeight="1">
-      <c r="A96" s="52" t="n">
-        <v>91</v>
-      </c>
-      <c r="B96" s="52" t="inlineStr">
+      <c r="G103" s="53" t="inlineStr"/>
+      <c r="H103" s="53" t="inlineStr"/>
+      <c r="I103" s="52" t="inlineStr"/>
+      <c r="J103" s="52" t="inlineStr"/>
+      <c r="K103" s="54" t="inlineStr"/>
+      <c r="L103" s="53" t="inlineStr"/>
+      <c r="M103" s="53" t="inlineStr"/>
+    </row>
+    <row r="104" ht="40" customHeight="1">
+      <c r="A104" s="52" t="n">
+        <v>99</v>
+      </c>
+      <c r="B104" s="52" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C96" s="53" t="inlineStr">
+      <c r="C104" s="53" t="inlineStr">
         <is>
           <t>Quota &amp; Chi phí</t>
         </is>
       </c>
-      <c r="D96" s="53" t="inlineStr">
+      <c r="D104" s="53" t="inlineStr">
         <is>
           <t>Sub-key API</t>
         </is>
       </c>
-      <c r="E96" s="53" t="inlineStr">
+      <c r="E104" s="53" t="inlineStr">
         <is>
           <t>Kiểm tra user có sub-key riêng</t>
         </is>
       </c>
-      <c r="F96" s="53" t="inlineStr">
+      <c r="F104" s="53" t="inlineStr">
         <is>
           <t>Mỗi user có key riêng</t>
         </is>
       </c>
-      <c r="G96" s="53" t="inlineStr"/>
-      <c r="H96" s="53" t="inlineStr"/>
-      <c r="I96" s="52" t="inlineStr"/>
-      <c r="J96" s="52" t="inlineStr"/>
-      <c r="K96" s="54" t="inlineStr"/>
-      <c r="L96" s="53" t="inlineStr"/>
-      <c r="M96" s="53" t="inlineStr"/>
-    </row>
-    <row r="97" ht="40" customHeight="1">
-      <c r="A97" s="55" t="n">
-        <v>92</v>
-      </c>
-      <c r="B97" s="55" t="inlineStr">
+      <c r="G104" s="53" t="inlineStr"/>
+      <c r="H104" s="53" t="inlineStr"/>
+      <c r="I104" s="52" t="inlineStr"/>
+      <c r="J104" s="52" t="inlineStr"/>
+      <c r="K104" s="54" t="inlineStr"/>
+      <c r="L104" s="53" t="inlineStr"/>
+      <c r="M104" s="53" t="inlineStr"/>
+    </row>
+    <row r="105" ht="40" customHeight="1">
+      <c r="A105" s="55" t="n">
+        <v>100</v>
+      </c>
+      <c r="B105" s="55" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C97" s="56" t="inlineStr">
+      <c r="C105" s="56" t="inlineStr">
         <is>
           <t>Cấu hình hệ thống</t>
         </is>
       </c>
-      <c r="D97" s="56" t="inlineStr">
+      <c r="D105" s="56" t="inlineStr">
         <is>
           <t>WebUI settings</t>
         </is>
       </c>
-      <c r="E97" s="56" t="inlineStr">
+      <c r="E105" s="56" t="inlineStr">
         <is>
           <t>Admin → Settings → General</t>
         </is>
       </c>
-      <c r="F97" s="56" t="inlineStr">
+      <c r="F105" s="56" t="inlineStr">
         <is>
           <t>Cấu hình lưu và áp dụng</t>
         </is>
       </c>
-      <c r="G97" s="56" t="inlineStr"/>
-      <c r="H97" s="56" t="inlineStr"/>
-      <c r="I97" s="55" t="inlineStr"/>
-      <c r="J97" s="55" t="inlineStr"/>
-      <c r="K97" s="57" t="inlineStr"/>
-      <c r="L97" s="56" t="inlineStr"/>
-      <c r="M97" s="56" t="inlineStr"/>
-    </row>
-    <row r="98" ht="40" customHeight="1">
-      <c r="A98" s="55" t="n">
-        <v>93</v>
-      </c>
-      <c r="B98" s="55" t="inlineStr">
+      <c r="G105" s="56" t="inlineStr"/>
+      <c r="H105" s="56" t="inlineStr"/>
+      <c r="I105" s="55" t="inlineStr"/>
+      <c r="J105" s="55" t="inlineStr"/>
+      <c r="K105" s="57" t="inlineStr"/>
+      <c r="L105" s="56" t="inlineStr"/>
+      <c r="M105" s="56" t="inlineStr"/>
+    </row>
+    <row r="106" ht="40" customHeight="1">
+      <c r="A106" s="55" t="n">
+        <v>101</v>
+      </c>
+      <c r="B106" s="55" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C98" s="56" t="inlineStr">
+      <c r="C106" s="56" t="inlineStr">
         <is>
           <t>Cấu hình hệ thống</t>
         </is>
       </c>
-      <c r="D98" s="56" t="inlineStr">
+      <c r="D106" s="56" t="inlineStr">
         <is>
           <t>Connections</t>
         </is>
       </c>
-      <c r="E98" s="56" t="inlineStr">
+      <c r="E106" s="56" t="inlineStr">
         <is>
           <t>Admin → Settings → Connections</t>
         </is>
       </c>
-      <c r="F98" s="56" t="inlineStr">
-        <is>
-          <t>Kết nối providers, status OK</t>
-        </is>
-      </c>
-      <c r="G98" s="56" t="inlineStr"/>
-      <c r="H98" s="56" t="inlineStr"/>
-      <c r="I98" s="55" t="inlineStr"/>
-      <c r="J98" s="55" t="inlineStr"/>
-      <c r="K98" s="57" t="inlineStr"/>
-      <c r="L98" s="56" t="inlineStr"/>
-      <c r="M98" s="56" t="inlineStr"/>
-    </row>
-    <row r="99" ht="40" customHeight="1">
-      <c r="A99" s="55" t="n">
-        <v>94</v>
-      </c>
-      <c r="B99" s="55" t="inlineStr">
+      <c r="F106" s="56" t="inlineStr">
+        <is>
+          <t>Kết nối 4 providers (OpenAI, Gemini, xAI, Anthropic), status OK</t>
+        </is>
+      </c>
+      <c r="G106" s="56" t="inlineStr"/>
+      <c r="H106" s="56" t="inlineStr"/>
+      <c r="I106" s="55" t="inlineStr"/>
+      <c r="J106" s="55" t="inlineStr"/>
+      <c r="K106" s="57" t="inlineStr"/>
+      <c r="L106" s="56" t="inlineStr"/>
+      <c r="M106" s="56" t="inlineStr"/>
+    </row>
+    <row r="107" ht="40" customHeight="1">
+      <c r="A107" s="55" t="n">
+        <v>102</v>
+      </c>
+      <c r="B107" s="55" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C99" s="56" t="inlineStr">
+      <c r="C107" s="56" t="inlineStr">
         <is>
           <t>Cấu hình hệ thống</t>
         </is>
       </c>
-      <c r="D99" s="56" t="inlineStr">
+      <c r="D107" s="56" t="inlineStr">
         <is>
           <t>RAG config</t>
         </is>
       </c>
-      <c r="E99" s="56" t="inlineStr">
+      <c r="E107" s="56" t="inlineStr">
         <is>
           <t>Điều chỉnh chunk size, file limit</t>
         </is>
       </c>
-      <c r="F99" s="56" t="inlineStr">
+      <c r="F107" s="56" t="inlineStr">
         <is>
           <t>Thay đổi được áp dụng</t>
         </is>
       </c>
-      <c r="G99" s="56" t="inlineStr"/>
-      <c r="H99" s="56" t="inlineStr"/>
-      <c r="I99" s="55" t="inlineStr"/>
-      <c r="J99" s="55" t="inlineStr"/>
-      <c r="K99" s="57" t="inlineStr"/>
-      <c r="L99" s="56" t="inlineStr"/>
-      <c r="M99" s="56" t="inlineStr"/>
-    </row>
-    <row r="100" ht="40" customHeight="1">
-      <c r="A100" s="55" t="n">
-        <v>95</v>
-      </c>
-      <c r="B100" s="55" t="inlineStr">
+      <c r="G107" s="56" t="inlineStr"/>
+      <c r="H107" s="56" t="inlineStr"/>
+      <c r="I107" s="55" t="inlineStr"/>
+      <c r="J107" s="55" t="inlineStr"/>
+      <c r="K107" s="57" t="inlineStr"/>
+      <c r="L107" s="56" t="inlineStr"/>
+      <c r="M107" s="56" t="inlineStr"/>
+    </row>
+    <row r="108" ht="40" customHeight="1">
+      <c r="A108" s="55" t="n">
+        <v>103</v>
+      </c>
+      <c r="B108" s="55" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C100" s="56" t="inlineStr">
+      <c r="C108" s="56" t="inlineStr">
         <is>
           <t>Cấu hình hệ thống</t>
         </is>
       </c>
-      <c r="D100" s="56" t="inlineStr">
+      <c r="D108" s="56" t="inlineStr">
         <is>
           <t>Signup control</t>
         </is>
       </c>
-      <c r="E100" s="56" t="inlineStr">
+      <c r="E108" s="56" t="inlineStr">
         <is>
           <t>Bật/tắt đăng ký mới</t>
         </is>
       </c>
-      <c r="F100" s="56" t="inlineStr">
+      <c r="F108" s="56" t="inlineStr">
         <is>
           <t>Đúng trạng thái bật/tắt</t>
         </is>
       </c>
-      <c r="G100" s="56" t="inlineStr"/>
-      <c r="H100" s="56" t="inlineStr"/>
-      <c r="I100" s="55" t="inlineStr"/>
-      <c r="J100" s="55" t="inlineStr"/>
-      <c r="K100" s="57" t="inlineStr"/>
-      <c r="L100" s="56" t="inlineStr"/>
-      <c r="M100" s="56" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="K101" s="58" t="n"/>
-    </row>
-    <row r="102">
-      <c r="K102" s="58" t="n"/>
-    </row>
-    <row r="103">
-      <c r="K103" s="58" t="n"/>
-    </row>
-    <row r="104">
-      <c r="K104" s="58" t="n"/>
-    </row>
-    <row r="105">
-      <c r="K105" s="58" t="n"/>
-    </row>
-    <row r="106">
-      <c r="K106" s="58" t="n"/>
-    </row>
-    <row r="107">
-      <c r="K107" s="58" t="n"/>
-    </row>
-    <row r="108">
-      <c r="K108" s="58" t="n"/>
+      <c r="G108" s="56" t="inlineStr"/>
+      <c r="H108" s="56" t="inlineStr"/>
+      <c r="I108" s="55" t="inlineStr"/>
+      <c r="J108" s="55" t="inlineStr"/>
+      <c r="K108" s="57" t="inlineStr"/>
+      <c r="L108" s="56" t="inlineStr"/>
+      <c r="M108" s="56" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="K109" s="58" t="n"/>
@@ -5011,15 +5283,39 @@
     <row r="150">
       <c r="K150" s="58" t="n"/>
     </row>
+    <row r="151">
+      <c r="K151" s="58" t="n"/>
+    </row>
+    <row r="152">
+      <c r="K152" s="58" t="n"/>
+    </row>
+    <row r="153">
+      <c r="K153" s="58" t="n"/>
+    </row>
+    <row r="154">
+      <c r="K154" s="58" t="n"/>
+    </row>
+    <row r="155">
+      <c r="K155" s="58" t="n"/>
+    </row>
+    <row r="156">
+      <c r="K156" s="58" t="n"/>
+    </row>
+    <row r="157">
+      <c r="K157" s="58" t="n"/>
+    </row>
+    <row r="158">
+      <c r="K158" s="58" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:M100"/>
+  <autoFilter ref="A3:M108"/>
   <mergeCells count="4">
     <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A85:M85"/>
     <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A77:M77"/>
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="I4:I150">
+  <conditionalFormatting sqref="I4:I158">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"PASS"</formula>
     </cfRule>
@@ -5034,10 +5330,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="I4:I150" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn PASS, FAIL, PARTIAL hoặc SKIP" promptTitle="Kết quả test" prompt="Chọn kết quả" type="list">
+    <dataValidation sqref="I4:I158" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn PASS, FAIL, PARTIAL hoặc SKIP" promptTitle="Kết quả test" prompt="Chọn kết quả" type="list">
       <formula1>"PASS,FAIL,PARTIAL,SKIP"</formula1>
     </dataValidation>
-    <dataValidation sqref="J4:J150" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="Chọn 1-5" type="list">
+    <dataValidation sqref="J4:J158" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="Chọn 1-5" type="list">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5198,7 +5494,7 @@
       </c>
       <c r="E4" s="60" t="inlineStr">
         <is>
-          <t>GPT-5</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
       <c r="F4" s="60" t="inlineStr">
@@ -5248,12 +5544,12 @@
       </c>
       <c r="E5" s="62" t="inlineStr">
         <is>
-          <t>Gemini 2.5 Pro</t>
+          <t>gemini-3.1-pro-preview</t>
         </is>
       </c>
       <c r="F5" s="62" t="inlineStr">
         <is>
-          <t>"Viết 3 mẫu quảng cáo Facebook cho đèn LED thông minh, tone chuyên nghiệp"</t>
+          <t>"Viết 3 mẫu quảng cáo Facebook cho đèn LED thông minh"</t>
         </is>
       </c>
       <c r="G5" s="62" t="inlineStr"/>
@@ -5290,7 +5586,7 @@
       </c>
       <c r="E6" s="60" t="inlineStr">
         <is>
-          <t>GPT-4.1</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
       <c r="F6" s="60" t="inlineStr">
@@ -5336,7 +5632,7 @@
       </c>
       <c r="E7" s="62" t="inlineStr">
         <is>
-          <t>GPT-5 Mini</t>
+          <t>gpt-5</t>
         </is>
       </c>
       <c r="F7" s="62" t="inlineStr">
@@ -5378,7 +5674,7 @@
       </c>
       <c r="E8" s="60" t="inlineStr">
         <is>
-          <t>GPT-5</t>
+          <t>grok-4.20-reasoning</t>
         </is>
       </c>
       <c r="F8" s="60" t="inlineStr">
@@ -6455,23 +6751,23 @@
         </is>
       </c>
       <c r="D4" s="68">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Hỏi đáp (Chat AI)")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Hỏi đáp (Chat AI)")</f>
         <v/>
       </c>
       <c r="E4" s="69">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Hỏi đáp (Chat AI)",'Form Test Tính Năng'!I$4:I$150,"PASS")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Hỏi đáp (Chat AI)",'Form Test Tính Năng'!I$4:I$158,"PASS")</f>
         <v/>
       </c>
       <c r="F4" s="70">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Hỏi đáp (Chat AI)",'Form Test Tính Năng'!I$4:I$150,"FAIL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Hỏi đáp (Chat AI)",'Form Test Tính Năng'!I$4:I$158,"FAIL")</f>
         <v/>
       </c>
       <c r="G4" s="71">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Hỏi đáp (Chat AI)",'Form Test Tính Năng'!I$4:I$150,"PARTIAL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Hỏi đáp (Chat AI)",'Form Test Tính Năng'!I$4:I$158,"PARTIAL")</f>
         <v/>
       </c>
       <c r="H4" s="72">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Hỏi đáp (Chat AI)",'Form Test Tính Năng'!I$4:I$150,"SKIP")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Hỏi đáp (Chat AI)",'Form Test Tính Năng'!I$4:I$158,"SKIP")</f>
         <v/>
       </c>
       <c r="I4" s="73">
@@ -6494,23 +6790,23 @@
         </is>
       </c>
       <c r="D5" s="74">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Tạo ảnh AI")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Tạo ảnh AI")</f>
         <v/>
       </c>
       <c r="E5" s="69">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Tạo ảnh AI",'Form Test Tính Năng'!I$4:I$150,"PASS")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Tạo ảnh AI",'Form Test Tính Năng'!I$4:I$158,"PASS")</f>
         <v/>
       </c>
       <c r="F5" s="70">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Tạo ảnh AI",'Form Test Tính Năng'!I$4:I$150,"FAIL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Tạo ảnh AI",'Form Test Tính Năng'!I$4:I$158,"FAIL")</f>
         <v/>
       </c>
       <c r="G5" s="71">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Tạo ảnh AI",'Form Test Tính Năng'!I$4:I$150,"PARTIAL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Tạo ảnh AI",'Form Test Tính Năng'!I$4:I$158,"PARTIAL")</f>
         <v/>
       </c>
       <c r="H5" s="72">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Tạo ảnh AI",'Form Test Tính Năng'!I$4:I$150,"SKIP")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Tạo ảnh AI",'Form Test Tính Năng'!I$4:I$158,"SKIP")</f>
         <v/>
       </c>
       <c r="I5" s="75">
@@ -6533,23 +6829,23 @@
         </is>
       </c>
       <c r="D6" s="68">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Gửi file &amp; truy xuất")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Gửi file &amp; truy xuất")</f>
         <v/>
       </c>
       <c r="E6" s="69">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Gửi file &amp; truy xuất",'Form Test Tính Năng'!I$4:I$150,"PASS")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Gửi file &amp; truy xuất",'Form Test Tính Năng'!I$4:I$158,"PASS")</f>
         <v/>
       </c>
       <c r="F6" s="70">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Gửi file &amp; truy xuất",'Form Test Tính Năng'!I$4:I$150,"FAIL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Gửi file &amp; truy xuất",'Form Test Tính Năng'!I$4:I$158,"FAIL")</f>
         <v/>
       </c>
       <c r="G6" s="71">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Gửi file &amp; truy xuất",'Form Test Tính Năng'!I$4:I$150,"PARTIAL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Gửi file &amp; truy xuất",'Form Test Tính Năng'!I$4:I$158,"PARTIAL")</f>
         <v/>
       </c>
       <c r="H6" s="72">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Gửi file &amp; truy xuất",'Form Test Tính Năng'!I$4:I$150,"SKIP")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Gửi file &amp; truy xuất",'Form Test Tính Năng'!I$4:I$158,"SKIP")</f>
         <v/>
       </c>
       <c r="I6" s="73">
@@ -6572,23 +6868,23 @@
         </is>
       </c>
       <c r="D7" s="74">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Chọn Model")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Chọn Model")</f>
         <v/>
       </c>
       <c r="E7" s="69">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Chọn Model",'Form Test Tính Năng'!I$4:I$150,"PASS")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Chọn Model",'Form Test Tính Năng'!I$4:I$158,"PASS")</f>
         <v/>
       </c>
       <c r="F7" s="70">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Chọn Model",'Form Test Tính Năng'!I$4:I$150,"FAIL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Chọn Model",'Form Test Tính Năng'!I$4:I$158,"FAIL")</f>
         <v/>
       </c>
       <c r="G7" s="71">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Chọn Model",'Form Test Tính Năng'!I$4:I$150,"PARTIAL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Chọn Model",'Form Test Tính Năng'!I$4:I$158,"PARTIAL")</f>
         <v/>
       </c>
       <c r="H7" s="72">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Chọn Model",'Form Test Tính Năng'!I$4:I$150,"SKIP")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Chọn Model",'Form Test Tính Năng'!I$4:I$158,"SKIP")</f>
         <v/>
       </c>
       <c r="I7" s="75">
@@ -6611,23 +6907,23 @@
         </is>
       </c>
       <c r="D8" s="68">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Kho kiến thức")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Kho kiến thức")</f>
         <v/>
       </c>
       <c r="E8" s="69">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Kho kiến thức",'Form Test Tính Năng'!I$4:I$150,"PASS")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Kho kiến thức",'Form Test Tính Năng'!I$4:I$158,"PASS")</f>
         <v/>
       </c>
       <c r="F8" s="70">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Kho kiến thức",'Form Test Tính Năng'!I$4:I$150,"FAIL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Kho kiến thức",'Form Test Tính Năng'!I$4:I$158,"FAIL")</f>
         <v/>
       </c>
       <c r="G8" s="71">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Kho kiến thức",'Form Test Tính Năng'!I$4:I$150,"PARTIAL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Kho kiến thức",'Form Test Tính Năng'!I$4:I$158,"PARTIAL")</f>
         <v/>
       </c>
       <c r="H8" s="72">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Kho kiến thức",'Form Test Tính Năng'!I$4:I$150,"SKIP")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Kho kiến thức",'Form Test Tính Năng'!I$4:I$158,"SKIP")</f>
         <v/>
       </c>
       <c r="I8" s="73">
@@ -6650,23 +6946,23 @@
         </is>
       </c>
       <c r="D9" s="74">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Không gian làm việc")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Không gian làm việc")</f>
         <v/>
       </c>
       <c r="E9" s="69">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Không gian làm việc",'Form Test Tính Năng'!I$4:I$150,"PASS")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Không gian làm việc",'Form Test Tính Năng'!I$4:I$158,"PASS")</f>
         <v/>
       </c>
       <c r="F9" s="70">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Không gian làm việc",'Form Test Tính Năng'!I$4:I$150,"FAIL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Không gian làm việc",'Form Test Tính Năng'!I$4:I$158,"FAIL")</f>
         <v/>
       </c>
       <c r="G9" s="71">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Không gian làm việc",'Form Test Tính Năng'!I$4:I$150,"PARTIAL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Không gian làm việc",'Form Test Tính Năng'!I$4:I$158,"PARTIAL")</f>
         <v/>
       </c>
       <c r="H9" s="72">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Không gian làm việc",'Form Test Tính Năng'!I$4:I$150,"SKIP")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Không gian làm việc",'Form Test Tính Năng'!I$4:I$158,"SKIP")</f>
         <v/>
       </c>
       <c r="I9" s="75">
@@ -6689,23 +6985,23 @@
         </is>
       </c>
       <c r="D10" s="68">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Giọng nói")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Giọng nói")</f>
         <v/>
       </c>
       <c r="E10" s="69">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Giọng nói",'Form Test Tính Năng'!I$4:I$150,"PASS")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Giọng nói",'Form Test Tính Năng'!I$4:I$158,"PASS")</f>
         <v/>
       </c>
       <c r="F10" s="70">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Giọng nói",'Form Test Tính Năng'!I$4:I$150,"FAIL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Giọng nói",'Form Test Tính Năng'!I$4:I$158,"FAIL")</f>
         <v/>
       </c>
       <c r="G10" s="71">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Giọng nói",'Form Test Tính Năng'!I$4:I$150,"PARTIAL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Giọng nói",'Form Test Tính Năng'!I$4:I$158,"PARTIAL")</f>
         <v/>
       </c>
       <c r="H10" s="72">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Giọng nói",'Form Test Tính Năng'!I$4:I$150,"SKIP")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Giọng nói",'Form Test Tính Năng'!I$4:I$158,"SKIP")</f>
         <v/>
       </c>
       <c r="I10" s="73">
@@ -6728,23 +7024,23 @@
         </is>
       </c>
       <c r="D11" s="74">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Tìm kiếm Web")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Tìm kiếm Web")</f>
         <v/>
       </c>
       <c r="E11" s="69">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Tìm kiếm Web",'Form Test Tính Năng'!I$4:I$150,"PASS")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Tìm kiếm Web",'Form Test Tính Năng'!I$4:I$158,"PASS")</f>
         <v/>
       </c>
       <c r="F11" s="70">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Tìm kiếm Web",'Form Test Tính Năng'!I$4:I$150,"FAIL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Tìm kiếm Web",'Form Test Tính Năng'!I$4:I$158,"FAIL")</f>
         <v/>
       </c>
       <c r="G11" s="71">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Tìm kiếm Web",'Form Test Tính Năng'!I$4:I$150,"PARTIAL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Tìm kiếm Web",'Form Test Tính Năng'!I$4:I$158,"PARTIAL")</f>
         <v/>
       </c>
       <c r="H11" s="72">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Tìm kiếm Web",'Form Test Tính Năng'!I$4:I$150,"SKIP")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Tìm kiếm Web",'Form Test Tính Năng'!I$4:I$158,"SKIP")</f>
         <v/>
       </c>
       <c r="I11" s="75">
@@ -6767,23 +7063,23 @@
         </is>
       </c>
       <c r="D12" s="68">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Giao diện &amp; Cá nhân hóa")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Giao diện &amp; Cá nhân hóa")</f>
         <v/>
       </c>
       <c r="E12" s="69">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Giao diện &amp; Cá nhân hóa",'Form Test Tính Năng'!I$4:I$150,"PASS")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Giao diện &amp; Cá nhân hóa",'Form Test Tính Năng'!I$4:I$158,"PASS")</f>
         <v/>
       </c>
       <c r="F12" s="70">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Giao diện &amp; Cá nhân hóa",'Form Test Tính Năng'!I$4:I$150,"FAIL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Giao diện &amp; Cá nhân hóa",'Form Test Tính Năng'!I$4:I$158,"FAIL")</f>
         <v/>
       </c>
       <c r="G12" s="71">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Giao diện &amp; Cá nhân hóa",'Form Test Tính Năng'!I$4:I$150,"PARTIAL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Giao diện &amp; Cá nhân hóa",'Form Test Tính Năng'!I$4:I$158,"PARTIAL")</f>
         <v/>
       </c>
       <c r="H12" s="72">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Giao diện &amp; Cá nhân hóa",'Form Test Tính Năng'!I$4:I$150,"SKIP")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Giao diện &amp; Cá nhân hóa",'Form Test Tính Năng'!I$4:I$158,"SKIP")</f>
         <v/>
       </c>
       <c r="I12" s="73">
@@ -6806,23 +7102,23 @@
         </is>
       </c>
       <c r="D13" s="74">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Quản lý người dùng")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Quản lý người dùng")</f>
         <v/>
       </c>
       <c r="E13" s="69">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Quản lý người dùng",'Form Test Tính Năng'!I$4:I$150,"PASS")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Quản lý người dùng",'Form Test Tính Năng'!I$4:I$158,"PASS")</f>
         <v/>
       </c>
       <c r="F13" s="70">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Quản lý người dùng",'Form Test Tính Năng'!I$4:I$150,"FAIL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Quản lý người dùng",'Form Test Tính Năng'!I$4:I$158,"FAIL")</f>
         <v/>
       </c>
       <c r="G13" s="71">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Quản lý người dùng",'Form Test Tính Năng'!I$4:I$150,"PARTIAL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Quản lý người dùng",'Form Test Tính Năng'!I$4:I$158,"PARTIAL")</f>
         <v/>
       </c>
       <c r="H13" s="72">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Quản lý người dùng",'Form Test Tính Năng'!I$4:I$150,"SKIP")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Quản lý người dùng",'Form Test Tính Năng'!I$4:I$158,"SKIP")</f>
         <v/>
       </c>
       <c r="I13" s="75">
@@ -6845,23 +7141,23 @@
         </is>
       </c>
       <c r="D14" s="68">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Quản lý Model")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Quản lý Model")</f>
         <v/>
       </c>
       <c r="E14" s="69">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Quản lý Model",'Form Test Tính Năng'!I$4:I$150,"PASS")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Quản lý Model",'Form Test Tính Năng'!I$4:I$158,"PASS")</f>
         <v/>
       </c>
       <c r="F14" s="70">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Quản lý Model",'Form Test Tính Năng'!I$4:I$150,"FAIL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Quản lý Model",'Form Test Tính Năng'!I$4:I$158,"FAIL")</f>
         <v/>
       </c>
       <c r="G14" s="71">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Quản lý Model",'Form Test Tính Năng'!I$4:I$150,"PARTIAL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Quản lý Model",'Form Test Tính Năng'!I$4:I$158,"PARTIAL")</f>
         <v/>
       </c>
       <c r="H14" s="72">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Quản lý Model",'Form Test Tính Năng'!I$4:I$150,"SKIP")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Quản lý Model",'Form Test Tính Năng'!I$4:I$158,"SKIP")</f>
         <v/>
       </c>
       <c r="I14" s="73">
@@ -6884,23 +7180,23 @@
         </is>
       </c>
       <c r="D15" s="74">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Dashboard &amp; Giám sát")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Dashboard &amp; Giám sát")</f>
         <v/>
       </c>
       <c r="E15" s="69">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Dashboard &amp; Giám sát",'Form Test Tính Năng'!I$4:I$150,"PASS")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Dashboard &amp; Giám sát",'Form Test Tính Năng'!I$4:I$158,"PASS")</f>
         <v/>
       </c>
       <c r="F15" s="70">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Dashboard &amp; Giám sát",'Form Test Tính Năng'!I$4:I$150,"FAIL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Dashboard &amp; Giám sát",'Form Test Tính Năng'!I$4:I$158,"FAIL")</f>
         <v/>
       </c>
       <c r="G15" s="71">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Dashboard &amp; Giám sát",'Form Test Tính Năng'!I$4:I$150,"PARTIAL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Dashboard &amp; Giám sát",'Form Test Tính Năng'!I$4:I$158,"PARTIAL")</f>
         <v/>
       </c>
       <c r="H15" s="72">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Dashboard &amp; Giám sát",'Form Test Tính Năng'!I$4:I$150,"SKIP")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Dashboard &amp; Giám sát",'Form Test Tính Năng'!I$4:I$158,"SKIP")</f>
         <v/>
       </c>
       <c r="I15" s="75">
@@ -6923,23 +7219,23 @@
         </is>
       </c>
       <c r="D16" s="68">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Quota &amp; Chi phí")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Quota &amp; Chi phí")</f>
         <v/>
       </c>
       <c r="E16" s="69">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Quota &amp; Chi phí",'Form Test Tính Năng'!I$4:I$150,"PASS")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Quota &amp; Chi phí",'Form Test Tính Năng'!I$4:I$158,"PASS")</f>
         <v/>
       </c>
       <c r="F16" s="70">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Quota &amp; Chi phí",'Form Test Tính Năng'!I$4:I$150,"FAIL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Quota &amp; Chi phí",'Form Test Tính Năng'!I$4:I$158,"FAIL")</f>
         <v/>
       </c>
       <c r="G16" s="71">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Quota &amp; Chi phí",'Form Test Tính Năng'!I$4:I$150,"PARTIAL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Quota &amp; Chi phí",'Form Test Tính Năng'!I$4:I$158,"PARTIAL")</f>
         <v/>
       </c>
       <c r="H16" s="72">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Quota &amp; Chi phí",'Form Test Tính Năng'!I$4:I$150,"SKIP")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Quota &amp; Chi phí",'Form Test Tính Năng'!I$4:I$158,"SKIP")</f>
         <v/>
       </c>
       <c r="I16" s="73">
@@ -6962,23 +7258,23 @@
         </is>
       </c>
       <c r="D17" s="74">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Cấu hình hệ thống")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Cấu hình hệ thống")</f>
         <v/>
       </c>
       <c r="E17" s="69">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Cấu hình hệ thống",'Form Test Tính Năng'!I$4:I$150,"PASS")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Cấu hình hệ thống",'Form Test Tính Năng'!I$4:I$158,"PASS")</f>
         <v/>
       </c>
       <c r="F17" s="70">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Cấu hình hệ thống",'Form Test Tính Năng'!I$4:I$150,"FAIL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Cấu hình hệ thống",'Form Test Tính Năng'!I$4:I$158,"FAIL")</f>
         <v/>
       </c>
       <c r="G17" s="71">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Cấu hình hệ thống",'Form Test Tính Năng'!I$4:I$150,"PARTIAL")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Cấu hình hệ thống",'Form Test Tính Năng'!I$4:I$158,"PARTIAL")</f>
         <v/>
       </c>
       <c r="H17" s="72">
-        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$150,"Cấu hình hệ thống",'Form Test Tính Năng'!I$4:I$150,"SKIP")</f>
+        <f>COUNTIFS('Form Test Tính Năng'!C$4:C$158,"Cấu hình hệ thống",'Form Test Tính Năng'!I$4:I$158,"SKIP")</f>
         <v/>
       </c>
       <c r="I17" s="75">
